--- a/data/complex_df_with_p_values.xlsx
+++ b/data/complex_df_with_p_values.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="309">
   <si>
     <t xml:space="preserve">Complex_ac</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t xml:space="preserve">SOFT_scaling_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARD_xc_epsilon_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFT_xc_epsilon_p</t>
   </si>
   <si>
     <t xml:space="preserve">CPX-1021</t>
@@ -1307,22 +1313,28 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -1331,10 +1343,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.194594968467493</v>
+        <v>0.193464425782302</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -1343,33 +1355,39 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.147426286856572</v>
+        <v>0.157421289355322</v>
       </c>
       <c r="M2" t="n">
-        <v>0.754622688655672</v>
+        <v>0.701149425287356</v>
       </c>
       <c r="N2" t="n">
-        <v>0.980509745127436</v>
+        <v>0.982008995502249</v>
       </c>
       <c r="O2" t="n">
-        <v>0.494752623688156</v>
+        <v>0.505747126436782</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.811094452773613</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
         <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -1378,10 +1396,10 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.194594968467493</v>
+        <v>0.193464425782302</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -1390,33 +1408,39 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.113943028485757</v>
+        <v>0.118940529735132</v>
       </c>
       <c r="M3" t="n">
-        <v>0.894552723638181</v>
+        <v>0.891554222888556</v>
       </c>
       <c r="N3" t="n">
-        <v>0.937531234382809</v>
+        <v>0.941529235382309</v>
       </c>
       <c r="O3" t="n">
-        <v>0.418790604697651</v>
+        <v>0.436281859070465</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.970514742628686</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -1425,10 +1449,10 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I4" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -1437,33 +1461,39 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.468765617191404</v>
+        <v>0.448775612193903</v>
       </c>
       <c r="M4" t="n">
-        <v>0.185907046476762</v>
+        <v>0.182908545727136</v>
       </c>
       <c r="N4" t="n">
-        <v>0.489755122438781</v>
+        <v>0.506246876561719</v>
       </c>
       <c r="O4" t="n">
-        <v>0.747626186906547</v>
+        <v>0.751124437781109</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.331834082958521</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F5" t="n">
         <v>9</v>
@@ -1472,45 +1502,51 @@
         <v>0.5625</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00772304598363456</v>
+        <v>0.000600431140180386</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.907218444322931</v>
       </c>
       <c r="J5" t="n">
-        <v>0.684354383553636</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.684354383553636</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0.000499750124937531</v>
       </c>
       <c r="M5" t="n">
-        <v>0.356821589205397</v>
+        <v>0.748125937031484</v>
       </c>
       <c r="N5" t="n">
-        <v>0.91704147926037</v>
+        <v>0.933533233383308</v>
       </c>
       <c r="O5" t="n">
-        <v>0.992503748125937</v>
+        <v>0.976011994002999</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.343328335832084</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
         <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
       </c>
       <c r="F6" t="n">
         <v>9</v>
@@ -1519,10 +1555,10 @@
         <v>0.5625</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00772304598363456</v>
+        <v>0.00755852475138584</v>
       </c>
       <c r="I6" t="n">
-        <v>0.908607832600671</v>
+        <v>0.907218444322931</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1531,33 +1567,39 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.000499750124937531</v>
       </c>
       <c r="M6" t="n">
-        <v>0.248875562218891</v>
+        <v>0.253373313343328</v>
       </c>
       <c r="N6" t="n">
-        <v>0.983008495752124</v>
+        <v>0.981009495252374</v>
       </c>
       <c r="O6" t="n">
-        <v>0.99400299850075</v>
+        <v>0.993503248375812</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.97996984848129</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.570714642678661</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -1566,10 +1608,10 @@
         <v>0.75</v>
       </c>
       <c r="H7" t="n">
-        <v>0.412311368641143</v>
+        <v>0.410412972613322</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.546497206046634</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1578,33 +1620,39 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.148425787106447</v>
+        <v>0.132433783108446</v>
       </c>
       <c r="M7" t="n">
-        <v>0.92703648175912</v>
+        <v>0.935532233883059</v>
       </c>
       <c r="N7" t="n">
-        <v>0.694152923538231</v>
+        <v>0.709145427286357</v>
       </c>
       <c r="O7" t="n">
-        <v>0.12143928035982</v>
+        <v>0.108945527236382</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.898550724637681</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s">
         <v>43</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>41</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -1613,10 +1661,10 @@
         <v>0.75</v>
       </c>
       <c r="H8" t="n">
-        <v>0.412311368641143</v>
+        <v>0.410412972613322</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0.546497206046634</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1625,33 +1673,39 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.239380309845077</v>
+        <v>0.296851574212894</v>
       </c>
       <c r="M8" t="n">
-        <v>0.638180909545227</v>
+        <v>0.530234882558721</v>
       </c>
       <c r="N8" t="n">
-        <v>0.974512743628186</v>
+        <v>0.965017491254373</v>
       </c>
       <c r="O8" t="n">
-        <v>0.500749625187406</v>
+        <v>0.478760619690155</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.710144927536232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1660,10 +1714,10 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.194594968467493</v>
+        <v>0.193464425782302</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1672,33 +1726,39 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0519740129935032</v>
+        <v>0.0264867566216892</v>
       </c>
       <c r="M9" t="n">
-        <v>0.634182908545727</v>
+        <v>0.628185907046477</v>
       </c>
       <c r="N9" t="n">
-        <v>0.847576211894053</v>
+        <v>0.841579210394803</v>
       </c>
       <c r="O9" t="n">
-        <v>0.565717141429285</v>
+        <v>0.609195402298851</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.744127936031984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -1710,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J10" t="n">
         <v>0.225577437233472</v>
@@ -1719,33 +1779,39 @@
         <v>0.225577437233472</v>
       </c>
       <c r="L10" t="n">
-        <v>0.954522738630685</v>
+        <v>0.965017491254373</v>
       </c>
       <c r="M10" t="n">
         <v>0.0239880059970015</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0344827586206897</v>
+        <v>0.0269865067466267</v>
       </c>
       <c r="O10" t="n">
-        <v>0.885557221389305</v>
+        <v>0.869565217391304</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.123411126417398</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.0359820089955022</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
         <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" t="s">
-        <v>54</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1757,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1766,33 +1832,39 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.513243378310845</v>
+        <v>0.523738130934533</v>
       </c>
       <c r="M11" t="n">
-        <v>0.857571214392804</v>
+        <v>0.867066466766617</v>
       </c>
       <c r="N11" t="n">
-        <v>0.417291354322839</v>
+        <v>0.418290854572714</v>
       </c>
       <c r="O11" t="n">
-        <v>0.00649675162418791</v>
+        <v>0.00499750124937531</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.650674662668666</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -1804,7 +1876,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1813,33 +1885,39 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0.728135932033983</v>
+        <v>0.738130934532734</v>
       </c>
       <c r="M12" t="n">
-        <v>0.740629685157421</v>
+        <v>0.733633183408296</v>
       </c>
       <c r="N12" t="n">
-        <v>0.288355822088956</v>
+        <v>0.275862068965517</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0239880059970015</v>
+        <v>0.031984007996002</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.504247876061969</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -1851,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.054100543368622</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1860,33 +1938,39 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.963018490754623</v>
+        <v>0.954022988505747</v>
       </c>
       <c r="M13" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.00249875062468766</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0789605197401299</v>
+        <v>0.0849575212393803</v>
       </c>
       <c r="O13" t="n">
-        <v>0.946026986506747</v>
+        <v>0.944527736131934</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.123411126417398</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.0169915042478761</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -1895,10 +1979,10 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J14" t="n">
         <v>0.225577437233472</v>
@@ -1907,33 +1991,39 @@
         <v>0.225577437233472</v>
       </c>
       <c r="L14" t="n">
-        <v>0.718140929535232</v>
+        <v>0.715142428785607</v>
       </c>
       <c r="M14" t="n">
-        <v>0.461769115442279</v>
+        <v>0.455272363818091</v>
       </c>
       <c r="N14" t="n">
-        <v>0.265867066466767</v>
+        <v>0.24487756121939</v>
       </c>
       <c r="O14" t="n">
-        <v>0.625687156421789</v>
+        <v>0.601699150424788</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.365817091454273</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
@@ -1942,10 +2032,10 @@
         <v>0.833333333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>0.945843094672941</v>
+        <v>0.945217008273597</v>
       </c>
       <c r="I15" t="n">
-        <v>0.734797298513648</v>
+        <v>0.732568713786491</v>
       </c>
       <c r="J15" t="n">
         <v>0.11209326076977</v>
@@ -1954,33 +2044,39 @@
         <v>0.11209326076977</v>
       </c>
       <c r="L15" t="n">
-        <v>0.88455772113943</v>
+        <v>0.887056471764118</v>
       </c>
       <c r="M15" t="n">
-        <v>0.389805097451274</v>
+        <v>0.381809095452274</v>
       </c>
       <c r="N15" t="n">
-        <v>0.144427786106947</v>
+        <v>0.134932533733133</v>
       </c>
       <c r="O15" t="n">
-        <v>0.135932033983008</v>
+        <v>0.128435782108946</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.237216862963837</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.255372313843078</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -1989,10 +2085,10 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I16" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2001,33 +2097,39 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.268865567216392</v>
+        <v>0.272863568215892</v>
       </c>
       <c r="M16" t="n">
-        <v>0.494252873563218</v>
+        <v>0.506246876561719</v>
       </c>
       <c r="N16" t="n">
-        <v>0.582208895552224</v>
+        <v>0.591204397801099</v>
       </c>
       <c r="O16" t="n">
-        <v>0.685157421289355</v>
+        <v>0.704647676161919</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.600199900049975</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -2036,10 +2138,10 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I17" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2048,33 +2150,39 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0.453273363318341</v>
+        <v>0.440279860069965</v>
       </c>
       <c r="M17" t="n">
-        <v>0.161419290354823</v>
+        <v>0.168415792103948</v>
       </c>
       <c r="N17" t="n">
-        <v>0.326336831584208</v>
+        <v>0.311844077961019</v>
       </c>
       <c r="O17" t="n">
         <v>0.670664667666167</v>
       </c>
+      <c r="P17" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.314342828585707</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -2083,10 +2191,10 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H18" t="n">
-        <v>0.594907706833053</v>
+        <v>0.592783601954566</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.651712185877717</v>
       </c>
       <c r="J18" t="n">
         <v>0.400479817844982</v>
@@ -2095,33 +2203,39 @@
         <v>0.400479817844982</v>
       </c>
       <c r="L18" t="n">
-        <v>0.738130934532734</v>
+        <v>0.71264367816092</v>
       </c>
       <c r="M18" t="n">
-        <v>0.275862068965517</v>
+        <v>0.27336331834083</v>
       </c>
       <c r="N18" t="n">
-        <v>0.235882058970515</v>
+        <v>0.289855072463768</v>
       </c>
       <c r="O18" t="n">
-        <v>0.658670664667666</v>
+        <v>0.658170914542729</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.823513108452599</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.245877061469265</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
@@ -2130,10 +2244,10 @@
         <v>0.75</v>
       </c>
       <c r="H19" t="n">
-        <v>0.412311368641143</v>
+        <v>0.410412972613322</v>
       </c>
       <c r="I19" t="n">
-        <v>0.548766608022225</v>
+        <v>0.546497206046634</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2142,33 +2256,39 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.245877061469265</v>
+        <v>0.227386306846577</v>
       </c>
       <c r="M19" t="n">
-        <v>0.256871564217891</v>
+        <v>0.290854572713643</v>
       </c>
       <c r="N19" t="n">
-        <v>0.532733633183408</v>
+        <v>0.531734132933533</v>
       </c>
       <c r="O19" t="n">
-        <v>0.560219890054973</v>
+        <v>0.571214392803598</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.727565869793893</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.418290854572714</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F20" t="n">
         <v>2</v>
@@ -2177,10 +2297,10 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.194594968467493</v>
+        <v>0.193464425782302</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2189,33 +2309,39 @@
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0.122938530734633</v>
+        <v>0.100449775112444</v>
       </c>
       <c r="M20" t="n">
-        <v>0.622188905547226</v>
+        <v>0.693153423288356</v>
       </c>
       <c r="N20" t="n">
-        <v>0.739130434782609</v>
+        <v>0.770114942528736</v>
       </c>
       <c r="O20" t="n">
-        <v>0.750624687656172</v>
+        <v>0.71864067966017</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.819590204897551</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F21" t="n">
         <v>2</v>
@@ -2224,10 +2350,10 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2236,33 +2362,39 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.382808595702149</v>
+        <v>0.386306846576712</v>
       </c>
       <c r="M21" t="n">
-        <v>0.596201899050475</v>
+        <v>0.564217891054473</v>
       </c>
       <c r="N21" t="n">
-        <v>0.341829085457271</v>
+        <v>0.340329835082459</v>
       </c>
       <c r="O21" t="n">
-        <v>0.207896051974013</v>
+        <v>0.216391804097951</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.546226886556722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F22" t="n">
         <v>2</v>
@@ -2271,10 +2403,10 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2283,33 +2415,39 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.572213893053473</v>
+        <v>0.591204397801099</v>
       </c>
       <c r="M22" t="n">
-        <v>0.639180409795102</v>
+        <v>0.654172913543228</v>
       </c>
       <c r="N22" t="n">
-        <v>0.274862568715642</v>
+        <v>0.264867566216892</v>
       </c>
       <c r="O22" t="n">
-        <v>0.103948025987006</v>
+        <v>0.0854572713643178</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.495752123938031</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F23" t="n">
         <v>3</v>
@@ -2321,7 +2459,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.546497206046634</v>
       </c>
       <c r="J23" t="n">
         <v>0.318587725760987</v>
@@ -2330,33 +2468,39 @@
         <v>0.318587725760987</v>
       </c>
       <c r="L23" t="n">
-        <v>0.978510744627686</v>
+        <v>0.971014492753623</v>
       </c>
       <c r="M23" t="n">
-        <v>0.294352823588206</v>
+        <v>0.343828085957021</v>
       </c>
       <c r="N23" t="n">
-        <v>0.00999500249875063</v>
+        <v>0.0109945027486257</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2023988005997</v>
+        <v>0.179410294852574</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.727565869793893</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.0624687656171914</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -2365,10 +2509,10 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -2377,33 +2521,39 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.288855572213893</v>
+        <v>0.294852573713143</v>
       </c>
       <c r="M24" t="n">
-        <v>0.997001499250375</v>
+        <v>0.995002498750625</v>
       </c>
       <c r="N24" t="n">
-        <v>0.664167916041979</v>
+        <v>0.667666166916542</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0879560219890055</v>
+        <v>0.0989505247376312</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.875562218890555</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E25" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
@@ -2415,7 +2565,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J25" t="n">
         <v>0.225577437233472</v>
@@ -2424,33 +2574,39 @@
         <v>0.225577437233472</v>
       </c>
       <c r="L25" t="n">
-        <v>0.702648675662169</v>
+        <v>0.719140429785107</v>
       </c>
       <c r="M25" t="n">
         <v>0.343328335832084</v>
       </c>
       <c r="N25" t="n">
-        <v>0.136431784107946</v>
+        <v>0.12143928035982</v>
       </c>
       <c r="O25" t="n">
-        <v>0.31384307846077</v>
+        <v>0.299350324837581</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.291354322838581</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -2459,10 +2615,10 @@
         <v>0.75</v>
       </c>
       <c r="H26" t="n">
-        <v>0.825877456307246</v>
+        <v>0.824673847438103</v>
       </c>
       <c r="I26" t="n">
-        <v>0.548766608022225</v>
+        <v>0.546497206046634</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -2471,33 +2627,39 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.693153423288356</v>
+        <v>0.694652673663168</v>
       </c>
       <c r="M26" t="n">
-        <v>0.365317341329335</v>
+        <v>0.334832583708146</v>
       </c>
       <c r="N26" t="n">
-        <v>0.506746626686657</v>
+        <v>0.508745627186407</v>
       </c>
       <c r="O26" t="n">
-        <v>0.44127936031984</v>
+        <v>0.408795602198901</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.727565869793893</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.423288355822089</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F27" t="n">
         <v>4</v>
@@ -2506,10 +2668,10 @@
         <v>0.8</v>
       </c>
       <c r="H27" t="n">
-        <v>0.594907706833053</v>
+        <v>0.592783601954566</v>
       </c>
       <c r="I27" t="n">
-        <v>0.654035066433492</v>
+        <v>0.651712185877717</v>
       </c>
       <c r="J27" t="n">
         <v>0.400479817844982</v>
@@ -2518,33 +2680,39 @@
         <v>0.400479817844982</v>
       </c>
       <c r="L27" t="n">
-        <v>0.624687656171914</v>
+        <v>0.598700649675162</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0289855072463768</v>
+        <v>0.0334832583708146</v>
       </c>
       <c r="N27" t="n">
-        <v>0.254372813593203</v>
+        <v>0.261869065467266</v>
       </c>
       <c r="O27" t="n">
-        <v>0.96751624187906</v>
+        <v>0.969515242378811</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.439724153817775</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.0654672663668166</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F28" t="n">
         <v>2</v>
@@ -2553,10 +2721,10 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.194594968467493</v>
+        <v>0.193464425782302</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -2565,33 +2733,39 @@
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.168915542228886</v>
+        <v>0.181409295352324</v>
       </c>
       <c r="M28" t="n">
-        <v>0.63768115942029</v>
+        <v>0.68015992003998</v>
       </c>
       <c r="N28" t="n">
-        <v>0.624687656171914</v>
+        <v>0.653173413293353</v>
       </c>
       <c r="O28" t="n">
-        <v>0.769615192403798</v>
+        <v>0.783108445777111</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.670664667666167</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F29" t="n">
         <v>2</v>
@@ -2600,10 +2774,10 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.194594968467493</v>
+        <v>0.193464425782302</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -2615,30 +2789,36 @@
         <v>0.195902048975512</v>
       </c>
       <c r="M29" t="n">
-        <v>0.145927036481759</v>
+        <v>0.15992003998001</v>
       </c>
       <c r="N29" t="n">
-        <v>0.618190904547726</v>
+        <v>0.636181909045477</v>
       </c>
       <c r="O29" t="n">
-        <v>0.942528735632184</v>
+        <v>0.937031484257871</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.294352823588206</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
@@ -2647,10 +2827,10 @@
         <v>0.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0.594907706833053</v>
+        <v>0.592783601954566</v>
       </c>
       <c r="I30" t="n">
-        <v>0.654035066433492</v>
+        <v>0.651712185877717</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -2659,33 +2839,39 @@
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0.135432283858071</v>
+        <v>0.159420289855072</v>
       </c>
       <c r="M30" t="n">
-        <v>0.732133933033483</v>
+        <v>0.671664167916042</v>
       </c>
       <c r="N30" t="n">
-        <v>0.949025487256372</v>
+        <v>0.930034982508746</v>
       </c>
       <c r="O30" t="n">
-        <v>0.532233883058471</v>
+        <v>0.549225387306347</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.823513108452599</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.83208395802099</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C31" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F31" t="n">
         <v>3</v>
@@ -2694,10 +2880,10 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.412311368641143</v>
+        <v>0.410412972613322</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0.546497206046634</v>
       </c>
       <c r="J31" t="n">
         <v>0.318587725760987</v>
@@ -2706,33 +2892,39 @@
         <v>0.318587725760987</v>
       </c>
       <c r="L31" t="n">
-        <v>0.398300849575212</v>
+        <v>0.409795102448776</v>
       </c>
       <c r="M31" t="n">
-        <v>0.778110944527736</v>
+        <v>0.806096951524238</v>
       </c>
       <c r="N31" t="n">
-        <v>0.400299850074962</v>
+        <v>0.404297851074463</v>
       </c>
       <c r="O31" t="n">
-        <v>0.297351324337831</v>
+        <v>0.292353823088456</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.727565869793893</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.662168915542229</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F32" t="n">
         <v>3</v>
@@ -2741,10 +2933,10 @@
         <v>0.6</v>
       </c>
       <c r="H32" t="n">
-        <v>0.412311368641143</v>
+        <v>0.410412972613322</v>
       </c>
       <c r="I32" t="n">
-        <v>0.548766608022225</v>
+        <v>0.546497206046634</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -2753,33 +2945,39 @@
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0734632683658171</v>
+        <v>0.0664667666166917</v>
       </c>
       <c r="M32" t="n">
-        <v>0.471264367816092</v>
+        <v>0.47376311844078</v>
       </c>
       <c r="N32" t="n">
-        <v>0.827586206896552</v>
+        <v>0.818590704647676</v>
       </c>
       <c r="O32" t="n">
-        <v>0.753623188405797</v>
+        <v>0.758120939530235</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.727565869793893</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.656171914042978</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F33" t="n">
         <v>2</v>
@@ -2788,10 +2986,10 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H33" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -2800,33 +2998,39 @@
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>0.118440779610195</v>
+        <v>0.12343828085957</v>
       </c>
       <c r="M33" t="n">
-        <v>0.760619690154923</v>
+        <v>0.746126936531734</v>
       </c>
       <c r="N33" t="n">
-        <v>0.690154922538731</v>
+        <v>0.683158420789605</v>
       </c>
       <c r="O33" t="n">
-        <v>0.134432783608196</v>
+        <v>0.148925537231384</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.741129435282359</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D34" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F34" t="n">
         <v>3</v>
@@ -2835,10 +3039,10 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.825877456307246</v>
+        <v>0.824673847438103</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.546497206046634</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -2847,33 +3051,39 @@
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0999500249875062</v>
+        <v>0.0889555222388806</v>
       </c>
       <c r="M34" t="n">
-        <v>0.903048475762119</v>
+        <v>0.886056971514243</v>
       </c>
       <c r="N34" t="n">
-        <v>0.743628185907046</v>
+        <v>0.745127436281859</v>
       </c>
       <c r="O34" t="n">
-        <v>0.0294852573713143</v>
+        <v>0.047976011994003</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.855572213893053</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C35" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D35" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E35" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -2882,10 +3092,10 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.825877456307246</v>
+        <v>0.824673847438103</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0.546497206046634</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -2897,30 +3107,36 @@
         <v>0.208895552223888</v>
       </c>
       <c r="M35" t="n">
-        <v>0.810094952523738</v>
+        <v>0.803098450774613</v>
       </c>
       <c r="N35" t="n">
-        <v>0.617191404297851</v>
+        <v>0.597701149425287</v>
       </c>
       <c r="O35" t="n">
-        <v>0.0754622688655672</v>
+        <v>0.105947026486757</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.760619690154923</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B36" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D36" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E36" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F36" t="n">
         <v>2</v>
@@ -2929,10 +3145,10 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H36" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -2941,33 +3157,39 @@
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.258870564717641</v>
+        <v>0.248875562218891</v>
       </c>
       <c r="M36" t="n">
-        <v>0.64767616191904</v>
+        <v>0.6031984007996</v>
       </c>
       <c r="N36" t="n">
-        <v>0.523738130934533</v>
+        <v>0.527236381809095</v>
       </c>
       <c r="O36" t="n">
-        <v>0.269365317341329</v>
+        <v>0.318340829585207</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.610194902548726</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B37" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C37" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D37" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F37" t="n">
         <v>2</v>
@@ -2979,7 +3201,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -2988,33 +3210,39 @@
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0.589205397301349</v>
+        <v>0.590704647676162</v>
       </c>
       <c r="M37" t="n">
-        <v>0.384307846076962</v>
+        <v>0.353323338330835</v>
       </c>
       <c r="N37" t="n">
-        <v>0.544727636181909</v>
+        <v>0.568215892053973</v>
       </c>
       <c r="O37" t="n">
-        <v>0.381309345327336</v>
+        <v>0.40279860069965</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.44127936031984</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C38" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D38" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F38" t="n">
         <v>2</v>
@@ -3026,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J38" t="n">
         <v>0.225577437233472</v>
@@ -3035,33 +3263,39 @@
         <v>0.225577437233472</v>
       </c>
       <c r="L38" t="n">
-        <v>0.949025487256372</v>
+        <v>0.946026986506747</v>
       </c>
       <c r="M38" t="n">
-        <v>0.102948525737131</v>
+        <v>0.109445277361319</v>
       </c>
       <c r="N38" t="n">
         <v>0.136931534232884</v>
       </c>
       <c r="O38" t="n">
-        <v>0.676661669165417</v>
+        <v>0.67616191904048</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.123411126417398</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.0734632683658171</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B39" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
@@ -3070,10 +3304,10 @@
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I39" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -3082,33 +3316,39 @@
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.55672163918041</v>
+        <v>0.568215892053973</v>
       </c>
       <c r="M39" t="n">
-        <v>0.349825087456272</v>
+        <v>0.298350824587706</v>
       </c>
       <c r="N39" t="n">
-        <v>0.67616191904048</v>
+        <v>0.665167416291854</v>
       </c>
       <c r="O39" t="n">
-        <v>0.498250874562719</v>
+        <v>0.501249375312344</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.464767616191904</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B40" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D40" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E40" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F40" t="n">
         <v>2</v>
@@ -3117,10 +3357,10 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>0.194594968467493</v>
+        <v>0.193464425782302</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -3129,33 +3369,39 @@
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>0.024487756121939</v>
+        <v>0.0334832583708146</v>
       </c>
       <c r="M40" t="n">
-        <v>0.523238380809595</v>
+        <v>0.516741629185407</v>
       </c>
       <c r="N40" t="n">
-        <v>0.854072963518241</v>
+        <v>0.845077461269365</v>
       </c>
       <c r="O40" t="n">
-        <v>0.708645677161419</v>
+        <v>0.727636181909045</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.658670664667666</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B41" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C41" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D41" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E41" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
@@ -3167,7 +3413,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -3176,33 +3422,39 @@
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>0.721139430284858</v>
+        <v>0.72063968015992</v>
       </c>
       <c r="M41" t="n">
-        <v>0.325337331334333</v>
+        <v>0.346326836581709</v>
       </c>
       <c r="N41" t="n">
-        <v>0.172913543228386</v>
+        <v>0.166416791604198</v>
       </c>
       <c r="O41" t="n">
-        <v>0.395302348825587</v>
+        <v>0.382308845577211</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.196901549225387</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B42" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C42" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E42" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
@@ -3211,10 +3463,10 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H42" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I42" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -3223,33 +3475,39 @@
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>0.826086956521739</v>
+        <v>0.822588705647176</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0.998500749625187</v>
       </c>
       <c r="N42" t="n">
-        <v>0.942028985507246</v>
+        <v>0.938030984507746</v>
       </c>
       <c r="O42" t="n">
-        <v>0.780609695152424</v>
+        <v>0.772613693153423</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.87656171914043</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B43" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C43" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D43" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E43" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
@@ -3261,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.548766608022225</v>
+        <v>0.546497206046634</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -3270,33 +3528,39 @@
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>0.606696651674163</v>
+        <v>0.623188405797101</v>
       </c>
       <c r="M43" t="n">
-        <v>0.556221889055472</v>
+        <v>0.538230884557721</v>
       </c>
       <c r="N43" t="n">
-        <v>0.271864067966017</v>
+        <v>0.268365817091454</v>
       </c>
       <c r="O43" t="n">
         <v>0.115942028985507</v>
       </c>
+      <c r="P43" t="n">
+        <v>0.727565869793893</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.40279860069965</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B44" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D44" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F44" t="n">
         <v>2</v>
@@ -3308,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J44" t="n">
         <v>0.225577437233472</v>
@@ -3317,33 +3581,39 @@
         <v>0.225577437233472</v>
       </c>
       <c r="L44" t="n">
-        <v>0.87856071964018</v>
+        <v>0.880059970014992</v>
       </c>
       <c r="M44" t="n">
-        <v>0.383808095952024</v>
+        <v>0.402298850574713</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0674662668665667</v>
+        <v>0.0604697651174413</v>
       </c>
       <c r="O44" t="n">
-        <v>0.072463768115942</v>
+        <v>0.0779610194902549</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.164417791104448</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B45" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C45" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D45" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F45" t="n">
         <v>2</v>
@@ -3352,10 +3622,10 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -3364,33 +3634,39 @@
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.254372813593203</v>
+        <v>0.261869065467266</v>
       </c>
       <c r="M45" t="n">
-        <v>0.865567216391804</v>
+        <v>0.871064467766117</v>
       </c>
       <c r="N45" t="n">
-        <v>0.532733633183408</v>
+        <v>0.531234382808596</v>
       </c>
       <c r="O45" t="n">
-        <v>0.0449775112443778</v>
+        <v>0.0419790104947526</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.754122938530735</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B46" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C46" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D46" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E46" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
@@ -3399,10 +3675,10 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.825877456307246</v>
+        <v>0.824673847438103</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.546497206046634</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -3411,33 +3687,39 @@
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0.411794102948526</v>
+        <v>0.419290354822589</v>
       </c>
       <c r="M46" t="n">
-        <v>0.894052973513243</v>
+        <v>0.902548725637181</v>
       </c>
       <c r="N46" t="n">
-        <v>0.449275362318841</v>
+        <v>0.44327836081959</v>
       </c>
       <c r="O46" t="n">
         <v>0.0114942528735632</v>
       </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.736131934032983</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B47" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C47" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D47" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F47" t="n">
         <v>2</v>
@@ -3449,7 +3731,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -3458,33 +3740,39 @@
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.408295852073963</v>
+        <v>0.480759620189905</v>
       </c>
       <c r="M47" t="n">
-        <v>0.854072963518241</v>
+        <v>0.812093953023488</v>
       </c>
       <c r="N47" t="n">
-        <v>0.546226886556722</v>
+        <v>0.509745127436282</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0419790104947526</v>
+        <v>0.0314842578710645</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.738130934532734</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B48" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C48" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D48" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
@@ -3496,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -3505,33 +3793,39 @@
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0.753623188405797</v>
+        <v>0.760119940029985</v>
       </c>
       <c r="M48" t="n">
-        <v>0.715642178910545</v>
+        <v>0.704147926036982</v>
       </c>
       <c r="N48" t="n">
-        <v>0.350824587706147</v>
+        <v>0.341329335332334</v>
       </c>
       <c r="O48" t="n">
-        <v>0.0254872563718141</v>
+        <v>0.0249875062468766</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.572713643178411</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B49" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C49" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D49" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F49" t="n">
         <v>2</v>
@@ -3540,10 +3834,10 @@
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -3552,33 +3846,39 @@
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.0664667666166917</v>
+        <v>0.0894552723638181</v>
       </c>
       <c r="M49" t="n">
-        <v>0.964017991004498</v>
+        <v>0.92103948025987</v>
       </c>
       <c r="N49" t="n">
-        <v>0.918040979510245</v>
+        <v>0.903048475762119</v>
       </c>
       <c r="O49" t="n">
-        <v>0.122438780609695</v>
+        <v>0.106446776611694</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.984007996001999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C50" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D50" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E50" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F50" t="n">
         <v>2</v>
@@ -3587,10 +3887,10 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
@@ -3599,33 +3899,39 @@
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0.269865067466267</v>
+        <v>0.264867566216892</v>
       </c>
       <c r="M50" t="n">
-        <v>0.818090954522739</v>
+        <v>0.794602698650675</v>
       </c>
       <c r="N50" t="n">
-        <v>0.637181409295352</v>
+        <v>0.664167916041979</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0909545227386307</v>
+        <v>0.0944527736131934</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.814092953523238</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B51" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C51" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D51" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E51" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
@@ -3637,7 +3943,7 @@
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.732568713786491</v>
       </c>
       <c r="J51" t="n">
         <v>0.11209326076977</v>
@@ -3646,33 +3952,39 @@
         <v>0.11209326076977</v>
       </c>
       <c r="L51" t="n">
-        <v>0.829085457271364</v>
+        <v>0.830084957521239</v>
       </c>
       <c r="M51" t="n">
         <v>0.64167916041979</v>
       </c>
       <c r="N51" t="n">
-        <v>0.0929535232383808</v>
+        <v>0.101949025487256</v>
       </c>
       <c r="O51" t="n">
-        <v>0.0424787606196902</v>
+        <v>0.0304847576211894</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.574729014387067</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.389305347326337</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B52" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C52" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D52" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E52" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F52" t="n">
         <v>2</v>
@@ -3684,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J52" t="n">
         <v>0.014319932875572</v>
@@ -3693,33 +4005,39 @@
         <v>0.014319932875572</v>
       </c>
       <c r="L52" t="n">
-        <v>0.938530734632684</v>
+        <v>0.944527736131934</v>
       </c>
       <c r="M52" t="n">
-        <v>0.386306846576712</v>
+        <v>0.40279860069965</v>
       </c>
       <c r="N52" t="n">
-        <v>0.0169915042478761</v>
+        <v>0.015992003998001</v>
       </c>
       <c r="O52" t="n">
-        <v>0.188905547226387</v>
+        <v>0.219890054972514</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.123411126417398</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.0659670164917541</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B53" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C53" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D53" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E53" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F53" t="n">
         <v>2</v>
@@ -3728,10 +4046,10 @@
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.194594968467493</v>
+        <v>0.193464425782302</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
@@ -3740,33 +4058,39 @@
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>0.0944527736131934</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="M53" t="n">
-        <v>0.455772113943028</v>
+        <v>0.452773613193403</v>
       </c>
       <c r="N53" t="n">
-        <v>0.785607196401799</v>
+        <v>0.773113443278361</v>
       </c>
       <c r="O53" t="n">
-        <v>0.787106446776612</v>
+        <v>0.808595702148926</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.580209895052474</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B54" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C54" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D54" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E54" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F54" t="n">
         <v>2</v>
@@ -3775,10 +4099,10 @@
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I54" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J54" t="n">
         <v>1</v>
@@ -3787,33 +4111,39 @@
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>0.652673663168416</v>
+        <v>0.604197901049475</v>
       </c>
       <c r="M54" t="n">
-        <v>0.159420289855072</v>
+        <v>0.162418790604698</v>
       </c>
       <c r="N54" t="n">
-        <v>0.545727136431784</v>
+        <v>0.567716141929036</v>
       </c>
       <c r="O54" t="n">
-        <v>0.903048475762119</v>
+        <v>0.87856071964018</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.299850074962519</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B55" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C55" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D55" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E55" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F55" t="n">
         <v>2</v>
@@ -3822,10 +4152,10 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>0.194594968467493</v>
+        <v>0.193464425782302</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -3834,33 +4164,39 @@
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>0.031984007996002</v>
+        <v>0.0489755122438781</v>
       </c>
       <c r="M55" t="n">
-        <v>0.903048475762119</v>
+        <v>0.870564717641179</v>
       </c>
       <c r="N55" t="n">
-        <v>0.971514242878561</v>
+        <v>0.966516741629185</v>
       </c>
       <c r="O55" t="n">
-        <v>0.387806096951524</v>
+        <v>0.418790604697651</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.963018490754623</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B56" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C56" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D56" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
@@ -3869,10 +4205,10 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I56" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -3881,33 +4217,39 @@
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>0.5992003998001</v>
+        <v>0.590704647676162</v>
       </c>
       <c r="M56" t="n">
-        <v>0.454772613693153</v>
+        <v>0.459270364817591</v>
       </c>
       <c r="N56" t="n">
-        <v>0.501249375312344</v>
+        <v>0.497251374312844</v>
       </c>
       <c r="O56" t="n">
-        <v>0.523238380809595</v>
+        <v>0.574712643678161</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.515742128935532</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B57" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C57" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D57" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E57" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F57" t="n">
         <v>2</v>
@@ -3919,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
@@ -3928,33 +4270,39 @@
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0.734632683658171</v>
+        <v>0.749625187406297</v>
       </c>
       <c r="M57" t="n">
-        <v>0.721639180409795</v>
+        <v>0.739630184907546</v>
       </c>
       <c r="N57" t="n">
-        <v>0.229885057471264</v>
+        <v>0.225887056471764</v>
       </c>
       <c r="O57" t="n">
-        <v>0.0539730134932534</v>
+        <v>0.0419790104947526</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.452773613193403</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B58" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C58" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D58" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E58" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F58" t="n">
         <v>2</v>
@@ -3963,10 +4311,10 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J58" t="n">
         <v>0.225577437233472</v>
@@ -3978,30 +4326,36 @@
         <v>0.775112443778111</v>
       </c>
       <c r="M58" t="n">
-        <v>0.385807096451774</v>
+        <v>0.380309845077461</v>
       </c>
       <c r="N58" t="n">
-        <v>0.203898050974513</v>
+        <v>0.199900049975012</v>
       </c>
       <c r="O58" t="n">
-        <v>0.640179910044978</v>
+        <v>0.685157421289355</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.246376811594203</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B59" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C59" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D59" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E59" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
@@ -4010,10 +4364,10 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H59" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I59" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J59" t="n">
         <v>1</v>
@@ -4022,33 +4376,39 @@
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0.749625187406297</v>
+        <v>0.720139930034983</v>
       </c>
       <c r="M59" t="n">
-        <v>0.223388305847076</v>
+        <v>0.252373813093453</v>
       </c>
       <c r="N59" t="n">
-        <v>0.501749125437281</v>
+        <v>0.535732133933034</v>
       </c>
       <c r="O59" t="n">
-        <v>0.95752123938031</v>
+        <v>0.946026986506747</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.407796101949025</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B60" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C60" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D60" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E60" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F60" t="n">
         <v>2</v>
@@ -4057,10 +4417,10 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H60" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J60" t="n">
         <v>0.225577437233472</v>
@@ -4069,33 +4429,39 @@
         <v>0.225577437233472</v>
       </c>
       <c r="L60" t="n">
-        <v>0.782108945527236</v>
+        <v>0.759620189905047</v>
       </c>
       <c r="M60" t="n">
-        <v>0.36431784107946</v>
+        <v>0.389805097451274</v>
       </c>
       <c r="N60" t="n">
         <v>0.2023988005997</v>
       </c>
       <c r="O60" t="n">
-        <v>0.64367816091954</v>
+        <v>0.667666166916542</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.259870064967516</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B61" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C61" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D61" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E61" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F61" t="n">
         <v>2</v>
@@ -4104,10 +4470,10 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J61" t="n">
         <v>0.225577437233472</v>
@@ -4116,33 +4482,39 @@
         <v>0.225577437233472</v>
       </c>
       <c r="L61" t="n">
-        <v>0.621689155422289</v>
+        <v>0.63568215892054</v>
       </c>
       <c r="M61" t="n">
-        <v>0.519740129935032</v>
+        <v>0.495252373813093</v>
       </c>
       <c r="N61" t="n">
-        <v>0.365317341329335</v>
+        <v>0.369815092453773</v>
       </c>
       <c r="O61" t="n">
-        <v>0.507746126936532</v>
+        <v>0.521239380309845</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.500749625187406</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B62" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C62" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D62" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F62" t="n">
         <v>2</v>
@@ -4154,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
@@ -4163,33 +4535,39 @@
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0.495252373813093</v>
+        <v>0.505247376311844</v>
       </c>
       <c r="M62" t="n">
-        <v>0.783108445777111</v>
+        <v>0.785107446276862</v>
       </c>
       <c r="N62" t="n">
-        <v>0.425287356321839</v>
+        <v>0.417291354322839</v>
       </c>
       <c r="O62" t="n">
-        <v>0.0704647676161919</v>
+        <v>0.0579710144927536</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.653173413293353</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B63" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C63" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E63" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
@@ -4201,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0.546497206046634</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
@@ -4210,33 +4588,39 @@
         <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0.500749625187406</v>
+        <v>0.460269865067466</v>
       </c>
       <c r="M63" t="n">
-        <v>0.918040979510245</v>
+        <v>0.927536231884058</v>
       </c>
       <c r="N63" t="n">
-        <v>0.515242378810595</v>
+        <v>0.541729135432284</v>
       </c>
       <c r="O63" t="n">
-        <v>0.000999500249875062</v>
+        <v>0.00149925037481259</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.804097951024488</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B64" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C64" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D64" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E64" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F64" t="n">
         <v>6</v>
@@ -4245,10 +4629,10 @@
         <v>0.6</v>
       </c>
       <c r="H64" t="n">
-        <v>0.540975290142877</v>
+        <v>0.538355651500659</v>
       </c>
       <c r="I64" t="n">
-        <v>0.425052830561442</v>
+        <v>0.794693999708677</v>
       </c>
       <c r="J64" t="n">
         <v>0.536043768902537</v>
@@ -4257,33 +4641,39 @@
         <v>0.536043768902537</v>
       </c>
       <c r="L64" t="n">
-        <v>0.653173413293353</v>
+        <v>0.613193403298351</v>
       </c>
       <c r="M64" t="n">
-        <v>0.0844577711144428</v>
+        <v>0.109945027486257</v>
       </c>
       <c r="N64" t="n">
-        <v>0.411294352823588</v>
+        <v>0.419290354822589</v>
       </c>
       <c r="O64" t="n">
-        <v>0.985007496251874</v>
+        <v>0.987006496751624</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.355802213463891</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.172913543228386</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B65" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C65" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D65" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E65" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F65" t="n">
         <v>4</v>
@@ -4292,10 +4682,10 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H65" t="n">
-        <v>0.902867372798644</v>
+        <v>0.901970595932615</v>
       </c>
       <c r="I65" t="n">
-        <v>0.232961232788422</v>
+        <v>0.651712185877717</v>
       </c>
       <c r="J65" t="n">
         <v>1</v>
@@ -4304,33 +4694,39 @@
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>0.640679660169915</v>
+        <v>0.668165917041479</v>
       </c>
       <c r="M65" t="n">
-        <v>0.260869565217391</v>
+        <v>0.254372813593203</v>
       </c>
       <c r="N65" t="n">
-        <v>0.546226886556722</v>
+        <v>0.529735132433783</v>
       </c>
       <c r="O65" t="n">
-        <v>0.861069465267366</v>
+        <v>0.854572713643178</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.439724153817775</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.383808095952024</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B66" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C66" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D66" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E66" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F66" t="n">
         <v>2</v>
@@ -4342,7 +4738,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
@@ -4351,33 +4747,39 @@
         <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>0.853073463268366</v>
+        <v>0.892053973013493</v>
       </c>
       <c r="M66" t="n">
-        <v>0.209895052473763</v>
+        <v>0.187406296851574</v>
       </c>
       <c r="N66" t="n">
-        <v>0.169415292353823</v>
+        <v>0.11544227886057</v>
       </c>
       <c r="O66" t="n">
-        <v>0.154922538730635</v>
+        <v>0.192903548225887</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.178910544727636</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B67" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C67" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D67" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E67" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F67" t="n">
         <v>13</v>
@@ -4386,10 +4788,10 @@
         <v>0.684210526315789</v>
       </c>
       <c r="H67" t="n">
-        <v>0.969554084685555</v>
+        <v>0.96892003547262</v>
       </c>
       <c r="I67" t="n">
-        <v>0.358137840987042</v>
+        <v>0.967911385386393</v>
       </c>
       <c r="J67" t="n">
         <v>1</v>
@@ -4398,33 +4800,39 @@
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.35432283858071</v>
+        <v>0.377811094452774</v>
       </c>
       <c r="M67" t="n">
-        <v>0.719140429785107</v>
+        <v>0.707646176911544</v>
       </c>
       <c r="N67" t="n">
-        <v>0.786106946526737</v>
+        <v>0.776611694152924</v>
       </c>
       <c r="O67" t="n">
-        <v>0.109445277361319</v>
+        <v>0.116941529235382</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.726527126840092</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.800099950024987</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B68" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C68" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D68" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E68" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F68" t="n">
         <v>4</v>
@@ -4433,10 +4841,10 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>0.594907706833053</v>
+        <v>0.592783601954566</v>
       </c>
       <c r="I68" t="n">
-        <v>0.654035066433492</v>
+        <v>0.651712185877717</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
@@ -4445,33 +4853,39 @@
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0.453773113443278</v>
+        <v>0.484757621189405</v>
       </c>
       <c r="M68" t="n">
-        <v>0.427786106946527</v>
+        <v>0.424287856071964</v>
       </c>
       <c r="N68" t="n">
-        <v>0.642678660669665</v>
+        <v>0.619690154922539</v>
       </c>
       <c r="O68" t="n">
-        <v>0.547226386806597</v>
+        <v>0.55272363818091</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.823513108452599</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.56071964017991</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B69" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C69" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D69" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
@@ -4480,10 +4894,10 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J69" t="n">
         <v>1</v>
@@ -4492,33 +4906,39 @@
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>0.561719140429785</v>
+        <v>0.571714142928536</v>
       </c>
       <c r="M69" t="n">
-        <v>0.512743628185907</v>
+        <v>0.520739630184908</v>
       </c>
       <c r="N69" t="n">
-        <v>0.531734132933533</v>
+        <v>0.519740129935032</v>
       </c>
       <c r="O69" t="n">
-        <v>0.297351324337831</v>
+        <v>0.277861069465267</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.544727636181909</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B70" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C70" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D70" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F70" t="n">
         <v>2</v>
@@ -4530,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J70" t="n">
         <v>0.225577437233472</v>
@@ -4539,33 +4959,39 @@
         <v>0.225577437233472</v>
       </c>
       <c r="L70" t="n">
-        <v>0.885057471264368</v>
+        <v>0.878060969515242</v>
       </c>
       <c r="M70" t="n">
-        <v>0.0999500249875062</v>
+        <v>0.116441779110445</v>
       </c>
       <c r="N70" t="n">
-        <v>0.112443778110945</v>
+        <v>0.111444277861069</v>
       </c>
       <c r="O70" t="n">
-        <v>0.72663668165917</v>
+        <v>0.703148425787106</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.123411126417398</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.0979510244877561</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B71" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C71" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D71" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
@@ -4574,10 +5000,10 @@
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J71" t="n">
         <v>0.225577437233472</v>
@@ -4586,33 +5012,39 @@
         <v>0.225577437233472</v>
       </c>
       <c r="L71" t="n">
-        <v>0.68415792103948</v>
+        <v>0.672663668165917</v>
       </c>
       <c r="M71" t="n">
-        <v>0.43928035982009</v>
+        <v>0.421289355322339</v>
       </c>
       <c r="N71" t="n">
-        <v>0.216891554222889</v>
+        <v>0.228885557221389</v>
       </c>
       <c r="O71" t="n">
-        <v>0.220889555222389</v>
+        <v>0.242378810594703</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.460269865067466</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B72" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C72" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D72" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E72" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F72" t="n">
         <v>2</v>
@@ -4621,10 +5053,10 @@
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0.688022093751878</v>
+        <v>0.686586889163176</v>
       </c>
       <c r="I72" t="n">
-        <v>0.411582586843052</v>
+        <v>0.40961216539683</v>
       </c>
       <c r="J72" t="n">
         <v>1</v>
@@ -4633,16 +5065,22 @@
         <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>0.428285857071464</v>
+        <v>0.463268365817091</v>
       </c>
       <c r="M72" t="n">
-        <v>0.702648675662169</v>
+        <v>0.665167416291854</v>
       </c>
       <c r="N72" t="n">
-        <v>0.759620189905047</v>
+        <v>0.754622688655672</v>
       </c>
       <c r="O72" t="n">
-        <v>0.515742128935532</v>
+        <v>0.512743628185907</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.579603626629426</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0.794602698650675</v>
       </c>
     </row>
   </sheetData>

--- a/data/complex_df_with_p_values.xlsx
+++ b/data/complex_df_with_p_values.xlsx
@@ -35,6 +35,9 @@
     <t xml:space="preserve">ratio_genes_exist</t>
   </si>
   <si>
+    <t xml:space="preserve">HARD_xc_epsilon_p</t>
+  </si>
+  <si>
     <t xml:space="preserve">HARD_eta_p</t>
   </si>
   <si>
@@ -57,9 +60,6 @@
   </si>
   <si>
     <t xml:space="preserve">SOFT_scaling_p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARD_xc_epsilon_p</t>
   </si>
   <si>
     <t xml:space="preserve">SOFT_xc_epsilon_p</t>
@@ -1343,34 +1343,34 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.193464425782302</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I2" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.157421289355322</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.701149425287356</v>
+        <v>0.142928535732134</v>
       </c>
       <c r="N2" t="n">
-        <v>0.982008995502249</v>
+        <v>0.692153923038481</v>
       </c>
       <c r="O2" t="n">
-        <v>0.505747126436782</v>
+        <v>0.869065467266367</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0.614692653673163</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.811094452773613</v>
+        <v>0.771114442778611</v>
       </c>
     </row>
     <row r="3">
@@ -1396,34 +1396,34 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.193464425782302</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I3" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0.300466626758702</v>
       </c>
       <c r="L3" t="n">
-        <v>0.118940529735132</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.891554222888556</v>
+        <v>0.276361819090455</v>
       </c>
       <c r="N3" t="n">
-        <v>0.941529235382309</v>
+        <v>0.67216391804098</v>
       </c>
       <c r="O3" t="n">
-        <v>0.436281859070465</v>
+        <v>0.315342328835582</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0.375312343828086</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.970514742628686</v>
+        <v>0.505747126436782</v>
       </c>
     </row>
     <row r="4">
@@ -1449,34 +1449,34 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I4" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.448775612193903</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.182908545727136</v>
+        <v>0.262368815592204</v>
       </c>
       <c r="N4" t="n">
-        <v>0.506246876561719</v>
+        <v>0.72263868065967</v>
       </c>
       <c r="O4" t="n">
-        <v>0.751124437781109</v>
+        <v>0.829585207396302</v>
       </c>
       <c r="P4" t="n">
-        <v>0.579603626629426</v>
+        <v>0.414292853573213</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.331834082958521</v>
+        <v>0.800599700149925</v>
       </c>
     </row>
     <row r="5">
@@ -1502,34 +1502,34 @@
         <v>0.5625</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000600431140180386</v>
+        <v>0.0016293116063111</v>
       </c>
       <c r="I5" t="n">
-        <v>0.907218444322931</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0.335790249468997</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0.00805470289817191</v>
       </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.000499750124937531</v>
       </c>
-      <c r="M5" t="n">
-        <v>0.748125937031484</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.933533233383308</v>
-      </c>
       <c r="O5" t="n">
-        <v>0.976011994002999</v>
+        <v>0.000499750124937531</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.35832083958021</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.343328335832084</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="6">
@@ -1555,34 +1555,34 @@
         <v>0.5625</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00755852475138584</v>
+        <v>0.0016293116063111</v>
       </c>
       <c r="I6" t="n">
-        <v>0.907218444322931</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.335790249468997</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.00805470289817191</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.000499750124937531</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.253373313343328</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.981009495252374</v>
-      </c>
       <c r="O6" t="n">
-        <v>0.993503248375812</v>
+        <v>0.000499750124937531</v>
       </c>
       <c r="P6" t="n">
-        <v>0.97996984848129</v>
+        <v>0.363318340829585</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.570714642678661</v>
+        <v>0.000499750124937531</v>
       </c>
     </row>
     <row r="7">
@@ -1608,10 +1608,10 @@
         <v>0.75</v>
       </c>
       <c r="H7" t="n">
-        <v>0.410412972613322</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.546497206046634</v>
+        <v>0.734784062780603</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1620,22 +1620,22 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.132433783108446</v>
+        <v>0.0630802617661833</v>
       </c>
       <c r="M7" t="n">
-        <v>0.935532233883059</v>
+        <v>0.144427786106947</v>
       </c>
       <c r="N7" t="n">
-        <v>0.709145427286357</v>
+        <v>0.949525237381309</v>
       </c>
       <c r="O7" t="n">
-        <v>0.108945527236382</v>
+        <v>0.695652173913043</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0.0559720139930035</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.898550724637681</v>
+        <v>0.861569215392304</v>
       </c>
     </row>
     <row r="8">
@@ -1661,34 +1661,34 @@
         <v>0.75</v>
       </c>
       <c r="H8" t="n">
-        <v>0.410412972613322</v>
+        <v>0.487003861409952</v>
       </c>
       <c r="I8" t="n">
-        <v>0.546497206046634</v>
+        <v>0.734784062780603</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.251732081772143</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.296851574212894</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.530234882558721</v>
+        <v>0.680659670164918</v>
       </c>
       <c r="N8" t="n">
-        <v>0.965017491254373</v>
+        <v>0.314342828585707</v>
       </c>
       <c r="O8" t="n">
-        <v>0.478760619690155</v>
+        <v>0.699150424787606</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0.964017991004498</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.710144927536232</v>
+        <v>0.471764117941029</v>
       </c>
     </row>
     <row r="9">
@@ -1714,34 +1714,34 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.193464425782302</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I9" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.026666150662722</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0264867566216892</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0.628185907046477</v>
+        <v>0.926536731634183</v>
       </c>
       <c r="N9" t="n">
-        <v>0.841579210394803</v>
+        <v>0.0424787606196902</v>
       </c>
       <c r="O9" t="n">
-        <v>0.609195402298851</v>
+        <v>0.0109945027486257</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0.264367816091954</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.744127936031984</v>
+        <v>0.0434782608695652</v>
       </c>
     </row>
     <row r="10">
@@ -1767,34 +1767,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I10" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.225577437233472</v>
+        <v>0.107294511721661</v>
       </c>
       <c r="K10" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.965017491254373</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0239880059970015</v>
+        <v>0.706146926536732</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0269865067466267</v>
+        <v>0.330834582708646</v>
       </c>
       <c r="O10" t="n">
-        <v>0.869565217391304</v>
+        <v>0.664667666166917</v>
       </c>
       <c r="P10" t="n">
-        <v>0.123411126417398</v>
+        <v>0.991004497751124</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0359820089955022</v>
+        <v>0.482758620689655</v>
       </c>
     </row>
     <row r="11">
@@ -1823,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.40961216539683</v>
+        <v>0.127501830029947</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1832,22 +1832,22 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.523738130934533</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0.867066466766617</v>
+        <v>0.00699650174912544</v>
       </c>
       <c r="N11" t="n">
-        <v>0.418290854572714</v>
+        <v>0.989005497251374</v>
       </c>
       <c r="O11" t="n">
-        <v>0.00499750124937531</v>
+        <v>0.909045477261369</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0.190404797601199</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.650674662668666</v>
+        <v>0.995002498750625</v>
       </c>
     </row>
     <row r="12">
@@ -1876,7 +1876,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.40961216539683</v>
+        <v>0.127501830029947</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1885,22 +1885,22 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0.738130934532734</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.733633183408296</v>
+        <v>0.0619690154922539</v>
       </c>
       <c r="N12" t="n">
-        <v>0.275862068965517</v>
+        <v>0.881559220389805</v>
       </c>
       <c r="O12" t="n">
-        <v>0.031984007996002</v>
+        <v>0.910544727636182</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0.397801099450275</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.504247876061969</v>
+        <v>0.925537231384308</v>
       </c>
     </row>
     <row r="13">
@@ -1926,34 +1926,34 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I13" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0.107294511721661</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.954022988505747</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.00249875062468766</v>
+        <v>0.623188405797101</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0849575212393803</v>
+        <v>0.489255372313843</v>
       </c>
       <c r="O13" t="n">
-        <v>0.944527736131934</v>
+        <v>0.746626686656672</v>
       </c>
       <c r="P13" t="n">
-        <v>0.123411126417398</v>
+        <v>0.972513743128436</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0169915042478761</v>
+        <v>0.623188405797101</v>
       </c>
     </row>
     <row r="14">
@@ -1979,34 +1979,34 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.686586889163176</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J14" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0.715142428785607</v>
+        <v>0.28309325502308</v>
       </c>
       <c r="M14" t="n">
-        <v>0.455272363818091</v>
+        <v>0.3928035982009</v>
       </c>
       <c r="N14" t="n">
-        <v>0.24487756121939</v>
+        <v>0.79960019990005</v>
       </c>
       <c r="O14" t="n">
-        <v>0.601699150424788</v>
+        <v>0.747126436781609</v>
       </c>
       <c r="P14" t="n">
-        <v>0.579603626629426</v>
+        <v>0.160419790104948</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.365817091454273</v>
+        <v>0.813593203398301</v>
       </c>
     </row>
     <row r="15">
@@ -2032,34 +2032,34 @@
         <v>0.833333333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>0.945217008273597</v>
+        <v>0.48374600885126</v>
       </c>
       <c r="I15" t="n">
-        <v>0.732568713786491</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.11209326076977</v>
+        <v>0.863159620211482</v>
       </c>
       <c r="K15" t="n">
-        <v>0.11209326076977</v>
+        <v>0.19007397503006</v>
       </c>
       <c r="L15" t="n">
-        <v>0.887056471764118</v>
+        <v>0.170567192713679</v>
       </c>
       <c r="M15" t="n">
-        <v>0.381809095452274</v>
+        <v>0.907046476761619</v>
       </c>
       <c r="N15" t="n">
-        <v>0.134932533733133</v>
+        <v>0.352823588205897</v>
       </c>
       <c r="O15" t="n">
-        <v>0.128435782108946</v>
+        <v>0.130934532733633</v>
       </c>
       <c r="P15" t="n">
-        <v>0.237216862963837</v>
+        <v>0.00599700149925037</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.255372313843078</v>
+        <v>0.167416291854073</v>
       </c>
     </row>
     <row r="16">
@@ -2085,34 +2085,34 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.686586889163176</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I16" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0.107294511721661</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.272863568215892</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>0.506246876561719</v>
+        <v>0.893553223388306</v>
       </c>
       <c r="N16" t="n">
-        <v>0.591204397801099</v>
+        <v>0.0484757621189405</v>
       </c>
       <c r="O16" t="n">
-        <v>0.704647676161919</v>
+        <v>0.237881059470265</v>
       </c>
       <c r="P16" t="n">
-        <v>0.579603626629426</v>
+        <v>0.902048975512244</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.600199900049975</v>
+        <v>0.112443778110945</v>
       </c>
     </row>
     <row r="17">
@@ -2138,34 +2138,34 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I17" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0.440279860069965</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0.168415792103948</v>
+        <v>0.443778110944528</v>
       </c>
       <c r="N17" t="n">
-        <v>0.311844077961019</v>
+        <v>0.211394302848576</v>
       </c>
       <c r="O17" t="n">
-        <v>0.670664667666167</v>
+        <v>0.451774112943528</v>
       </c>
       <c r="P17" t="n">
-        <v>0.579603626629426</v>
+        <v>0.72663668165917</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.314342828585707</v>
+        <v>0.346326836581709</v>
       </c>
     </row>
     <row r="18">
@@ -2191,34 +2191,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H18" t="n">
-        <v>0.592783601954566</v>
+        <v>0.299375686270464</v>
       </c>
       <c r="I18" t="n">
-        <v>0.651712185877717</v>
+        <v>0.829723186836647</v>
       </c>
       <c r="J18" t="n">
-        <v>0.400479817844982</v>
+        <v>0.105948531795098</v>
       </c>
       <c r="K18" t="n">
-        <v>0.400479817844982</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.71264367816092</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0.27336331834083</v>
+        <v>0.903048475762119</v>
       </c>
       <c r="N18" t="n">
-        <v>0.289855072463768</v>
+        <v>0.0379810094952524</v>
       </c>
       <c r="O18" t="n">
-        <v>0.658170914542729</v>
+        <v>0.273863068465767</v>
       </c>
       <c r="P18" t="n">
-        <v>0.823513108452599</v>
+        <v>0.949025487256372</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.245877061469265</v>
+        <v>0.103948025987006</v>
       </c>
     </row>
     <row r="19">
@@ -2244,34 +2244,34 @@
         <v>0.75</v>
       </c>
       <c r="H19" t="n">
-        <v>0.410412972613322</v>
+        <v>0.868637116987786</v>
       </c>
       <c r="I19" t="n">
-        <v>0.546497206046634</v>
+        <v>0.291608231686989</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0.415033749543885</v>
       </c>
       <c r="L19" t="n">
-        <v>0.227386306846577</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>0.290854572713643</v>
+        <v>0.397301349325337</v>
       </c>
       <c r="N19" t="n">
-        <v>0.531734132933533</v>
+        <v>0.47976011994003</v>
       </c>
       <c r="O19" t="n">
-        <v>0.571214392803598</v>
+        <v>0.399800099950025</v>
       </c>
       <c r="P19" t="n">
-        <v>0.727565869793893</v>
+        <v>0.347826086956522</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.418290854572714</v>
+        <v>0.55672163918041</v>
       </c>
     </row>
     <row r="20">
@@ -2297,34 +2297,34 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.193464425782302</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I20" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0.300466626758702</v>
       </c>
       <c r="L20" t="n">
-        <v>0.100449775112444</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0.693153423288356</v>
+        <v>0.924037981009495</v>
       </c>
       <c r="N20" t="n">
-        <v>0.770114942528736</v>
+        <v>0.0559720139930035</v>
       </c>
       <c r="O20" t="n">
-        <v>0.71864067966017</v>
+        <v>0.0834582708645677</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>0.71264367816092</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.819590204897551</v>
+        <v>0.071464267866067</v>
       </c>
     </row>
     <row r="21">
@@ -2350,34 +2350,34 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I21" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0.300466626758702</v>
       </c>
       <c r="L21" t="n">
-        <v>0.386306846576712</v>
+        <v>0.28309325502308</v>
       </c>
       <c r="M21" t="n">
-        <v>0.564217891054473</v>
+        <v>0.776611694152924</v>
       </c>
       <c r="N21" t="n">
-        <v>0.340329835082459</v>
+        <v>0.359320339830085</v>
       </c>
       <c r="O21" t="n">
-        <v>0.216391804097951</v>
+        <v>0.0939530234882559</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0.0599700149925037</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.546226886556722</v>
+        <v>0.205897051474263</v>
       </c>
     </row>
     <row r="22">
@@ -2403,34 +2403,34 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I22" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.591204397801099</v>
+        <v>0.28309325502308</v>
       </c>
       <c r="M22" t="n">
-        <v>0.654172913543228</v>
+        <v>0.763618190904548</v>
       </c>
       <c r="N22" t="n">
-        <v>0.264867566216892</v>
+        <v>0.280359820089955</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0854572713643178</v>
+        <v>0.171914042978511</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>0.0934532733633183</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.495752123938031</v>
+        <v>0.219390304847576</v>
       </c>
     </row>
     <row r="23">
@@ -2456,34 +2456,34 @@
         <v>0.75</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0.868637116987786</v>
       </c>
       <c r="I23" t="n">
-        <v>0.546497206046634</v>
+        <v>0.291608231686989</v>
       </c>
       <c r="J23" t="n">
-        <v>0.318587725760987</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0.318587725760987</v>
+        <v>0.415033749543885</v>
       </c>
       <c r="L23" t="n">
-        <v>0.971014492753623</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>0.343828085957021</v>
+        <v>0.27936031984008</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0109945027486257</v>
+        <v>0.761619190404798</v>
       </c>
       <c r="O23" t="n">
-        <v>0.179410294852574</v>
+        <v>0.574712643678161</v>
       </c>
       <c r="P23" t="n">
-        <v>0.727565869793893</v>
+        <v>0.536231884057971</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0624687656171914</v>
+        <v>0.702648675662169</v>
       </c>
     </row>
     <row r="24">
@@ -2509,34 +2509,34 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.686586889163176</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I24" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0.026666150662722</v>
       </c>
       <c r="L24" t="n">
-        <v>0.294852573713143</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0.995002498750625</v>
+        <v>0.916041979010495</v>
       </c>
       <c r="N24" t="n">
-        <v>0.667666166916542</v>
+        <v>0.139430284857571</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0989505247376312</v>
+        <v>0.0109945027486257</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>0.240379810094953</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.875562218890555</v>
+        <v>0.0719640179910045</v>
       </c>
     </row>
     <row r="25">
@@ -2562,34 +2562,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I25" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J25" t="n">
-        <v>0.225577437233472</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K25" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.719140429785107</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0.343328335832084</v>
+        <v>0.144927536231884</v>
       </c>
       <c r="N25" t="n">
-        <v>0.12143928035982</v>
+        <v>0.756121939030485</v>
       </c>
       <c r="O25" t="n">
-        <v>0.299350324837581</v>
+        <v>0.900549725137431</v>
       </c>
       <c r="P25" t="n">
-        <v>0.579603626629426</v>
+        <v>0.671164417791104</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.291354322838581</v>
+        <v>0.833583208395802</v>
       </c>
     </row>
     <row r="26">
@@ -2615,34 +2615,34 @@
         <v>0.75</v>
       </c>
       <c r="H26" t="n">
-        <v>0.824673847438103</v>
+        <v>0.487003861409952</v>
       </c>
       <c r="I26" t="n">
-        <v>0.546497206046634</v>
+        <v>0.734784062780603</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0.696514834251129</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0.415033749543885</v>
       </c>
       <c r="L26" t="n">
-        <v>0.694652673663168</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0.334832583708146</v>
+        <v>0.533733133433283</v>
       </c>
       <c r="N26" t="n">
-        <v>0.508745627186407</v>
+        <v>0.567216391804098</v>
       </c>
       <c r="O26" t="n">
         <v>0.408795602198901</v>
       </c>
       <c r="P26" t="n">
-        <v>0.727565869793893</v>
+        <v>0.768615692153923</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.423288355822089</v>
+        <v>0.455272363818091</v>
       </c>
     </row>
     <row r="27">
@@ -2668,34 +2668,34 @@
         <v>0.8</v>
       </c>
       <c r="H27" t="n">
-        <v>0.592783601954566</v>
+        <v>0.299375686270464</v>
       </c>
       <c r="I27" t="n">
-        <v>0.651712185877717</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>0.400479817844982</v>
+        <v>0.105948531795098</v>
       </c>
       <c r="K27" t="n">
-        <v>0.400479817844982</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0.598700649675162</v>
+        <v>0.486286777422666</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0334832583708146</v>
+        <v>0.84407796101949</v>
       </c>
       <c r="N27" t="n">
-        <v>0.261869065467266</v>
+        <v>0.162418790604698</v>
       </c>
       <c r="O27" t="n">
-        <v>0.969515242378811</v>
+        <v>0.227386306846577</v>
       </c>
       <c r="P27" t="n">
-        <v>0.439724153817775</v>
+        <v>0.657671164417791</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.0654672663668166</v>
+        <v>0.223388305847076</v>
       </c>
     </row>
     <row r="28">
@@ -2721,34 +2721,34 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.193464425782302</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I28" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0.107294511721661</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.181409295352324</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0.68015992003998</v>
+        <v>0.903048475762119</v>
       </c>
       <c r="N28" t="n">
-        <v>0.653173413293353</v>
+        <v>0.0719640179910045</v>
       </c>
       <c r="O28" t="n">
-        <v>0.783108445777111</v>
+        <v>0.28735632183908</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0.929535232383808</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.670664667666167</v>
+        <v>0.137431284357821</v>
       </c>
     </row>
     <row r="29">
@@ -2774,34 +2774,34 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.193464425782302</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I29" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.107294511721661</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.195902048975512</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0.15992003998001</v>
+        <v>0.989005497251374</v>
       </c>
       <c r="N29" t="n">
-        <v>0.636181909045477</v>
+        <v>0.0304847576211894</v>
       </c>
       <c r="O29" t="n">
-        <v>0.937031484257871</v>
+        <v>0.0934532733633183</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>0.804597701149425</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.294352823588206</v>
+        <v>0.0904547726136932</v>
       </c>
     </row>
     <row r="30">
@@ -2827,34 +2827,34 @@
         <v>0.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0.592783601954566</v>
+        <v>0.933305477133902</v>
       </c>
       <c r="I30" t="n">
-        <v>0.651712185877717</v>
+        <v>0.133249772761508</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0.796181235085109</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0.159420289855072</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>0.671664167916042</v>
+        <v>0.143428285857071</v>
       </c>
       <c r="N30" t="n">
-        <v>0.930034982508746</v>
+        <v>0.685657171414293</v>
       </c>
       <c r="O30" t="n">
-        <v>0.549225387306347</v>
+        <v>0.934532733633183</v>
       </c>
       <c r="P30" t="n">
-        <v>0.823513108452599</v>
+        <v>0.819590204897551</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.83208395802099</v>
+        <v>0.823088455772114</v>
       </c>
     </row>
     <row r="31">
@@ -2880,34 +2880,34 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.410412972613322</v>
+        <v>0.11838083045409</v>
       </c>
       <c r="I31" t="n">
-        <v>0.546497206046634</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0.318587725760987</v>
+        <v>0.696514834251129</v>
       </c>
       <c r="K31" t="n">
-        <v>0.318587725760987</v>
+        <v>0.0713323811883347</v>
       </c>
       <c r="L31" t="n">
-        <v>0.409795102448776</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>0.806096951524238</v>
+        <v>0.965017491254373</v>
       </c>
       <c r="N31" t="n">
-        <v>0.404297851074463</v>
+        <v>0.0864567716141929</v>
       </c>
       <c r="O31" t="n">
-        <v>0.292353823088456</v>
+        <v>0.0204897551224388</v>
       </c>
       <c r="P31" t="n">
-        <v>0.727565869793893</v>
+        <v>0.407796101949025</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.662168915542229</v>
+        <v>0.0334832583708146</v>
       </c>
     </row>
     <row r="32">
@@ -2933,34 +2933,34 @@
         <v>0.6</v>
       </c>
       <c r="H32" t="n">
-        <v>0.410412972613322</v>
+        <v>0.487003861409952</v>
       </c>
       <c r="I32" t="n">
-        <v>0.546497206046634</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0.251732081772143</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0664667666166917</v>
+        <v>0.393099751651528</v>
       </c>
       <c r="M32" t="n">
-        <v>0.47376311844078</v>
+        <v>0.800099950024987</v>
       </c>
       <c r="N32" t="n">
-        <v>0.818590704647676</v>
+        <v>0.221889055472264</v>
       </c>
       <c r="O32" t="n">
-        <v>0.758120939530235</v>
+        <v>0.257371314342829</v>
       </c>
       <c r="P32" t="n">
-        <v>0.727565869793893</v>
+        <v>0.365317341329335</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.656171914042978</v>
+        <v>0.290354822588706</v>
       </c>
     </row>
     <row r="33">
@@ -2986,34 +2986,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H33" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I33" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0.300466626758702</v>
       </c>
       <c r="L33" t="n">
-        <v>0.12343828085957</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>0.746126936531734</v>
+        <v>0.329335332333833</v>
       </c>
       <c r="N33" t="n">
-        <v>0.683158420789605</v>
+        <v>0.381309345327336</v>
       </c>
       <c r="O33" t="n">
-        <v>0.148925537231384</v>
+        <v>0.284857571214393</v>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>0.354822588705647</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.741129435282359</v>
+        <v>0.448275862068966</v>
       </c>
     </row>
     <row r="34">
@@ -3039,34 +3039,34 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.824673847438103</v>
+        <v>0.868637116987786</v>
       </c>
       <c r="I34" t="n">
-        <v>0.546497206046634</v>
+        <v>0.291608231686989</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0.415033749543885</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0889555222388806</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0.886056971514243</v>
+        <v>0.0809595202398801</v>
       </c>
       <c r="N34" t="n">
-        <v>0.745127436281859</v>
+        <v>0.64767616191904</v>
       </c>
       <c r="O34" t="n">
-        <v>0.047976011994003</v>
+        <v>0.509745127436282</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>0.269865067466267</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.855572213893053</v>
+        <v>0.742628685657171</v>
       </c>
     </row>
     <row r="35">
@@ -3092,34 +3092,34 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.824673847438103</v>
+        <v>0.868637116987786</v>
       </c>
       <c r="I35" t="n">
-        <v>0.546497206046634</v>
+        <v>0.291608231686989</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0.415033749543885</v>
       </c>
       <c r="L35" t="n">
-        <v>0.208895552223888</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0.803098450774613</v>
+        <v>0.215892053973014</v>
       </c>
       <c r="N35" t="n">
-        <v>0.597701149425287</v>
+        <v>0.506746626686657</v>
       </c>
       <c r="O35" t="n">
-        <v>0.105947026486757</v>
+        <v>0.488755622188906</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0.484257871064468</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.760619690154923</v>
+        <v>0.612693653173413</v>
       </c>
     </row>
     <row r="36">
@@ -3145,34 +3145,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H36" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I36" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0.300466626758702</v>
       </c>
       <c r="L36" t="n">
-        <v>0.248875562218891</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6031984007996</v>
+        <v>0.60119940029985</v>
       </c>
       <c r="N36" t="n">
-        <v>0.527236381809095</v>
+        <v>0.24287856071964</v>
       </c>
       <c r="O36" t="n">
-        <v>0.318340829585207</v>
+        <v>0.286356821589205</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0.605697151424288</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.610194902548726</v>
+        <v>0.323338330834583</v>
       </c>
     </row>
     <row r="37">
@@ -3198,34 +3198,34 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I37" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0.590704647676162</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0.353323338330835</v>
+        <v>0.273863068465767</v>
       </c>
       <c r="N37" t="n">
-        <v>0.568215892053973</v>
+        <v>0.5952023988006</v>
       </c>
       <c r="O37" t="n">
-        <v>0.40279860069965</v>
+        <v>0.694152923538231</v>
       </c>
       <c r="P37" t="n">
-        <v>0.579603626629426</v>
+        <v>0.431284357821089</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.44127936031984</v>
+        <v>0.658670664667666</v>
       </c>
     </row>
     <row r="38">
@@ -3251,34 +3251,34 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I38" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J38" t="n">
-        <v>0.225577437233472</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K38" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.946026986506747</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>0.109445277361319</v>
+        <v>0.529735132433783</v>
       </c>
       <c r="N38" t="n">
-        <v>0.136931534232884</v>
+        <v>0.440279860069965</v>
       </c>
       <c r="O38" t="n">
-        <v>0.67616191904048</v>
+        <v>0.731134432783608</v>
       </c>
       <c r="P38" t="n">
-        <v>0.123411126417398</v>
+        <v>0.893053473263368</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0734632683658171</v>
+        <v>0.578210894552724</v>
       </c>
     </row>
     <row r="39">
@@ -3304,34 +3304,34 @@
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I39" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.568215892053973</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>0.298350824587706</v>
+        <v>0.472763618190905</v>
       </c>
       <c r="N39" t="n">
-        <v>0.665167416291854</v>
+        <v>0.44727636181909</v>
       </c>
       <c r="O39" t="n">
-        <v>0.501249375312344</v>
+        <v>0.768115942028985</v>
       </c>
       <c r="P39" t="n">
-        <v>0.579603626629426</v>
+        <v>0.877061469265367</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.464767616191904</v>
+        <v>0.590204897551224</v>
       </c>
     </row>
     <row r="40">
@@ -3357,34 +3357,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>0.193464425782302</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I40" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0.300466626758702</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0334832583708146</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0.516741629185407</v>
+        <v>0.95552223888056</v>
       </c>
       <c r="N40" t="n">
-        <v>0.845077461269365</v>
+        <v>0.0129935032483758</v>
       </c>
       <c r="O40" t="n">
-        <v>0.727636181909045</v>
+        <v>0.00549725137431284</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>0.380809595202399</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.658670664667666</v>
+        <v>0.024487756121939</v>
       </c>
     </row>
     <row r="41">
@@ -3410,34 +3410,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I41" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>0.72063968015992</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0.346326836581709</v>
+        <v>0.72263868065967</v>
       </c>
       <c r="N41" t="n">
-        <v>0.166416791604198</v>
+        <v>0.19240379810095</v>
       </c>
       <c r="O41" t="n">
-        <v>0.382308845577211</v>
+        <v>0.47376311844078</v>
       </c>
       <c r="P41" t="n">
-        <v>0.579603626629426</v>
+        <v>0.87856071964018</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.196901549225387</v>
+        <v>0.286356821589205</v>
       </c>
     </row>
     <row r="42">
@@ -3463,34 +3463,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H42" t="n">
-        <v>0.686586889163176</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I42" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0.300466626758702</v>
       </c>
       <c r="L42" t="n">
-        <v>0.822588705647176</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>0.998500749625187</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>0.938030984507746</v>
+        <v>0.424787606196902</v>
       </c>
       <c r="O42" t="n">
-        <v>0.772613693153423</v>
+        <v>0.501749125437281</v>
       </c>
       <c r="P42" t="n">
-        <v>0.579603626629426</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.87656171914043</v>
+        <v>0.307346326836582</v>
       </c>
     </row>
     <row r="43">
@@ -3516,34 +3516,34 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0.868637116987786</v>
       </c>
       <c r="I43" t="n">
-        <v>0.546497206046634</v>
+        <v>0.291608231686989</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0.696514834251129</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>0.623188405797101</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>0.538230884557721</v>
+        <v>0.341829085457271</v>
       </c>
       <c r="N43" t="n">
-        <v>0.268365817091454</v>
+        <v>0.420289855072464</v>
       </c>
       <c r="O43" t="n">
-        <v>0.115942028985507</v>
+        <v>0.715642178910545</v>
       </c>
       <c r="P43" t="n">
-        <v>0.727565869793893</v>
+        <v>0.790104947526237</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.40279860069965</v>
+        <v>0.584707646176912</v>
       </c>
     </row>
     <row r="44">
@@ -3572,31 +3572,31 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.880059970014992</v>
+        <v>0.0234002514704269</v>
       </c>
       <c r="M44" t="n">
-        <v>0.402298850574713</v>
+        <v>0.52423788105947</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0604697651174413</v>
+        <v>0.835582208895552</v>
       </c>
       <c r="O44" t="n">
-        <v>0.0779610194902549</v>
+        <v>0.386306846576712</v>
       </c>
       <c r="P44" t="n">
-        <v>0.579603626629426</v>
+        <v>0.0199900049975013</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.164417791104448</v>
+        <v>0.614192903548226</v>
       </c>
     </row>
     <row r="45">
@@ -3622,10 +3622,10 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.686586889163176</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -3634,22 +3634,22 @@
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.261869065467266</v>
+        <v>0.0234002514704269</v>
       </c>
       <c r="M45" t="n">
-        <v>0.871064467766117</v>
+        <v>0.376311844077961</v>
       </c>
       <c r="N45" t="n">
-        <v>0.531234382808596</v>
+        <v>0.818590704647676</v>
       </c>
       <c r="O45" t="n">
-        <v>0.0419790104947526</v>
+        <v>0.43528235882059</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>0.0264867566216892</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.754122938530735</v>
+        <v>0.676661669165417</v>
       </c>
     </row>
     <row r="46">
@@ -3675,10 +3675,10 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.824673847438103</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0.546497206046634</v>
+        <v>0.734784062780603</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -3687,22 +3687,22 @@
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0.419290354822589</v>
+        <v>0.0630802617661833</v>
       </c>
       <c r="M46" t="n">
-        <v>0.902548725637181</v>
+        <v>0.156921539230385</v>
       </c>
       <c r="N46" t="n">
-        <v>0.44327836081959</v>
+        <v>0.92103948025987</v>
       </c>
       <c r="O46" t="n">
-        <v>0.0114942528735632</v>
+        <v>0.68815592203898</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>0.0514742628685657</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.736131934032983</v>
+        <v>0.857571214392804</v>
       </c>
     </row>
     <row r="47">
@@ -3731,7 +3731,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.40961216539683</v>
+        <v>0.127501830029947</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -3740,22 +3740,22 @@
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.480759620189905</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.812093953023488</v>
+        <v>0.0754622688655672</v>
       </c>
       <c r="N47" t="n">
-        <v>0.509745127436282</v>
+        <v>0.855072463768116</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0314842578710645</v>
+        <v>0.971014492753623</v>
       </c>
       <c r="P47" t="n">
-        <v>1</v>
+        <v>0.568215892053973</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.738130934532734</v>
+        <v>0.926536731634183</v>
       </c>
     </row>
     <row r="48">
@@ -3784,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.40961216539683</v>
+        <v>0.127501830029947</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -3793,22 +3793,22 @@
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0.760119940029985</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0.704147926036982</v>
+        <v>0.133433283358321</v>
       </c>
       <c r="N48" t="n">
-        <v>0.341329335332334</v>
+        <v>0.805097451274363</v>
       </c>
       <c r="O48" t="n">
-        <v>0.0249875062468766</v>
+        <v>0.923538230884558</v>
       </c>
       <c r="P48" t="n">
-        <v>1</v>
+        <v>0.642178910544728</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.572713643178411</v>
+        <v>0.879060469765117</v>
       </c>
     </row>
     <row r="49">
@@ -3834,10 +3834,10 @@
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>0.686586889163176</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.40961216539683</v>
+        <v>0.127501830029947</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -3846,22 +3846,22 @@
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.0894552723638181</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0.92103948025987</v>
+        <v>0.0424787606196902</v>
       </c>
       <c r="N49" t="n">
-        <v>0.903048475762119</v>
+        <v>0.87256371814093</v>
       </c>
       <c r="O49" t="n">
-        <v>0.106446776611694</v>
+        <v>0.972513743128436</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>0.469265367316342</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.984007996001999</v>
+        <v>0.931534232883558</v>
       </c>
     </row>
     <row r="50">
@@ -3887,10 +3887,10 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0.686586889163176</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0.40961216539683</v>
+        <v>0.127501830029947</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
@@ -3899,22 +3899,22 @@
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0.264867566216892</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.794602698650675</v>
+        <v>0.0939530234882559</v>
       </c>
       <c r="N50" t="n">
-        <v>0.664167916041979</v>
+        <v>0.798100949525237</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0944527736131934</v>
+        <v>0.91904047976012</v>
       </c>
       <c r="P50" t="n">
-        <v>1</v>
+        <v>0.55272363818091</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.814092953523238</v>
+        <v>0.869065467266367</v>
       </c>
     </row>
     <row r="51">
@@ -3940,34 +3940,34 @@
         <v>0.833333333333333</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0.966159499330321</v>
       </c>
       <c r="I51" t="n">
-        <v>0.732568713786491</v>
+        <v>0.0578894771956845</v>
       </c>
       <c r="J51" t="n">
-        <v>0.11209326076977</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0.11209326076977</v>
+        <v>0.591105307782166</v>
       </c>
       <c r="L51" t="n">
-        <v>0.830084957521239</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.64167916041979</v>
+        <v>0.0889555222388806</v>
       </c>
       <c r="N51" t="n">
-        <v>0.101949025487256</v>
+        <v>0.924537731134433</v>
       </c>
       <c r="O51" t="n">
-        <v>0.0304847576211894</v>
+        <v>0.869065467266367</v>
       </c>
       <c r="P51" t="n">
-        <v>0.574729014387067</v>
+        <v>0.392303848075962</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.389305347326337</v>
+        <v>0.905547226386807</v>
       </c>
     </row>
     <row r="52">
@@ -3993,34 +3993,34 @@
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I52" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>0.014319932875572</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K52" t="n">
-        <v>0.014319932875572</v>
+        <v>0.300466626758702</v>
       </c>
       <c r="L52" t="n">
-        <v>0.944527736131934</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.40279860069965</v>
+        <v>0.881059470264868</v>
       </c>
       <c r="N52" t="n">
-        <v>0.015992003998001</v>
+        <v>0.156421789105447</v>
       </c>
       <c r="O52" t="n">
-        <v>0.219890054972514</v>
+        <v>0.107446276861569</v>
       </c>
       <c r="P52" t="n">
-        <v>0.123411126417398</v>
+        <v>0.386806596701649</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.0659670164917541</v>
+        <v>0.0909545227386307</v>
       </c>
     </row>
     <row r="53">
@@ -4046,34 +4046,34 @@
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.193464425782302</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I53" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0.300466626758702</v>
       </c>
       <c r="L53" t="n">
-        <v>0.103448275862069</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.452773613193403</v>
+        <v>0.967016491754123</v>
       </c>
       <c r="N53" t="n">
-        <v>0.773113443278361</v>
+        <v>0.0314842578710645</v>
       </c>
       <c r="O53" t="n">
-        <v>0.808595702148926</v>
+        <v>0.0594702648675662</v>
       </c>
       <c r="P53" t="n">
-        <v>1</v>
+        <v>0.690654672663668</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.580209895052474</v>
+        <v>0.0634682658670665</v>
       </c>
     </row>
     <row r="54">
@@ -4099,34 +4099,34 @@
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I54" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>0.604197901049475</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.162418790604698</v>
+        <v>0.320839580209895</v>
       </c>
       <c r="N54" t="n">
-        <v>0.567716141929036</v>
+        <v>0.666166916541729</v>
       </c>
       <c r="O54" t="n">
-        <v>0.87856071964018</v>
+        <v>0.854072963518241</v>
       </c>
       <c r="P54" t="n">
-        <v>0.579603626629426</v>
+        <v>0.806596701649175</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.299850074962519</v>
+        <v>0.756621689155422</v>
       </c>
     </row>
     <row r="55">
@@ -4152,10 +4152,10 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>0.193464425782302</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0.40961216539683</v>
+        <v>0.127501830029947</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -4164,22 +4164,22 @@
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>0.0489755122438781</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.870564717641179</v>
+        <v>0.0494752623688156</v>
       </c>
       <c r="N55" t="n">
-        <v>0.966516741629185</v>
+        <v>0.939030484757621</v>
       </c>
       <c r="O55" t="n">
-        <v>0.418790604697651</v>
+        <v>0.92703648175912</v>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>0.217391304347826</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.963018490754623</v>
+        <v>0.95352323838081</v>
       </c>
     </row>
     <row r="56">
@@ -4205,34 +4205,34 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I56" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0.300466626758702</v>
       </c>
       <c r="L56" t="n">
-        <v>0.590704647676162</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0.459270364817591</v>
+        <v>0.537731134432784</v>
       </c>
       <c r="N56" t="n">
-        <v>0.497251374312844</v>
+        <v>0.367316341829085</v>
       </c>
       <c r="O56" t="n">
-        <v>0.574712643678161</v>
+        <v>0.1984007996002</v>
       </c>
       <c r="P56" t="n">
-        <v>0.579603626629426</v>
+        <v>0.640179910044978</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.515742128935532</v>
+        <v>0.343328335832084</v>
       </c>
     </row>
     <row r="57">
@@ -4261,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0.40961216539683</v>
+        <v>0.127501830029947</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
@@ -4270,22 +4270,22 @@
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0.749625187406297</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.739630184907546</v>
+        <v>0.031984007996002</v>
       </c>
       <c r="N57" t="n">
-        <v>0.225887056471764</v>
+        <v>0.992003998000999</v>
       </c>
       <c r="O57" t="n">
-        <v>0.0419790104947526</v>
+        <v>0.864567716141929</v>
       </c>
       <c r="P57" t="n">
-        <v>1</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.452773613193403</v>
+        <v>0.979510244877561</v>
       </c>
     </row>
     <row r="58">
@@ -4311,34 +4311,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I58" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J58" t="n">
-        <v>0.225577437233472</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K58" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>0.775112443778111</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.380309845077461</v>
+        <v>0.456271864067966</v>
       </c>
       <c r="N58" t="n">
-        <v>0.199900049975012</v>
+        <v>0.400299850074962</v>
       </c>
       <c r="O58" t="n">
-        <v>0.685157421289355</v>
+        <v>0.609195402298851</v>
       </c>
       <c r="P58" t="n">
-        <v>0.579603626629426</v>
+        <v>0.750624687656172</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.246376811594203</v>
+        <v>0.540229885057471</v>
       </c>
     </row>
     <row r="59">
@@ -4364,34 +4364,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H59" t="n">
-        <v>0.686586889163176</v>
+        <v>0.241255174106044</v>
       </c>
       <c r="I59" t="n">
-        <v>0.40961216539683</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0.107294511721661</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0.720139930034983</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.252373813093453</v>
+        <v>0.754122938530735</v>
       </c>
       <c r="N59" t="n">
-        <v>0.535732133933034</v>
+        <v>0.138430784607696</v>
       </c>
       <c r="O59" t="n">
-        <v>0.946026986506747</v>
+        <v>0.435782108945527</v>
       </c>
       <c r="P59" t="n">
-        <v>0.579603626629426</v>
+        <v>0.966516741629185</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.407796101949025</v>
+        <v>0.230384807596202</v>
       </c>
     </row>
     <row r="60">
@@ -4417,34 +4417,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H60" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I60" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J60" t="n">
-        <v>0.225577437233472</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K60" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>0.759620189905047</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>0.389805097451274</v>
+        <v>0.443778110944528</v>
       </c>
       <c r="N60" t="n">
-        <v>0.2023988005997</v>
+        <v>0.427786106946527</v>
       </c>
       <c r="O60" t="n">
-        <v>0.667666166916542</v>
+        <v>0.631684157921039</v>
       </c>
       <c r="P60" t="n">
-        <v>0.579603626629426</v>
+        <v>0.749625187406297</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.259870064967516</v>
+        <v>0.559720139930035</v>
       </c>
     </row>
     <row r="61">
@@ -4470,34 +4470,34 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0.686586889163176</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J61" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.63568215892054</v>
+        <v>0.28309325502308</v>
       </c>
       <c r="M61" t="n">
-        <v>0.495252373813093</v>
+        <v>0.589705147426287</v>
       </c>
       <c r="N61" t="n">
-        <v>0.369815092453773</v>
+        <v>0.661669165417291</v>
       </c>
       <c r="O61" t="n">
-        <v>0.521239380309845</v>
+        <v>0.563718140929535</v>
       </c>
       <c r="P61" t="n">
-        <v>0.579603626629426</v>
+        <v>0.345327336331834</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.500749625187406</v>
+        <v>0.60119940029985</v>
       </c>
     </row>
     <row r="62">
@@ -4526,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.40961216539683</v>
+        <v>0.127501830029947</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
@@ -4535,22 +4535,22 @@
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0.505247376311844</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>0.785107446276862</v>
+        <v>0.047976011994003</v>
       </c>
       <c r="N62" t="n">
-        <v>0.417291354322839</v>
+        <v>0.903548225887057</v>
       </c>
       <c r="O62" t="n">
-        <v>0.0579710144927536</v>
+        <v>0.938530734632684</v>
       </c>
       <c r="P62" t="n">
-        <v>1</v>
+        <v>0.419290354822589</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.653173413293353</v>
+        <v>0.954522738630685</v>
       </c>
     </row>
     <row r="63">
@@ -4579,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.546497206046634</v>
+        <v>0.0454486292014263</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
@@ -4588,22 +4588,22 @@
         <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0.460269865067466</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>0.927536231884058</v>
+        <v>0.00549725137431284</v>
       </c>
       <c r="N63" t="n">
-        <v>0.541729135432284</v>
+        <v>0.985007496251874</v>
       </c>
       <c r="O63" t="n">
-        <v>0.00149925037481259</v>
+        <v>0.985507246376812</v>
       </c>
       <c r="P63" t="n">
-        <v>1</v>
+        <v>0.346326836581709</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.804097951024488</v>
+        <v>0.996501749125437</v>
       </c>
     </row>
     <row r="64">
@@ -4629,34 +4629,34 @@
         <v>0.6</v>
       </c>
       <c r="H64" t="n">
-        <v>0.538355651500659</v>
+        <v>0.101025331722206</v>
       </c>
       <c r="I64" t="n">
-        <v>0.794693999708677</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>0.536043768902537</v>
+        <v>0.0163234852503589</v>
       </c>
       <c r="K64" t="n">
-        <v>0.536043768902537</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.613193403298351</v>
+        <v>0.632062839743509</v>
       </c>
       <c r="M64" t="n">
-        <v>0.109945027486257</v>
+        <v>0.955022488755622</v>
       </c>
       <c r="N64" t="n">
-        <v>0.419290354822589</v>
+        <v>0.0304847576211894</v>
       </c>
       <c r="O64" t="n">
-        <v>0.987006496751624</v>
+        <v>0.11744127936032</v>
       </c>
       <c r="P64" t="n">
-        <v>0.355802213463891</v>
+        <v>0.862568715642179</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.172913543228386</v>
+        <v>0.0619690154922539</v>
       </c>
     </row>
     <row r="65">
@@ -4682,34 +4682,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H65" t="n">
-        <v>0.901970595932615</v>
+        <v>0.0580492118486313</v>
       </c>
       <c r="I65" t="n">
-        <v>0.651712185877717</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0.105948531795098</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0.510899041231745</v>
       </c>
       <c r="L65" t="n">
-        <v>0.668165917041479</v>
+        <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>0.254372813593203</v>
+        <v>0.952023988005997</v>
       </c>
       <c r="N65" t="n">
-        <v>0.529735132433783</v>
+        <v>0.0699650174912544</v>
       </c>
       <c r="O65" t="n">
-        <v>0.854572713643178</v>
+        <v>0.2063968015992</v>
       </c>
       <c r="P65" t="n">
-        <v>0.439724153817775</v>
+        <v>0.911044477761119</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.383808095952024</v>
+        <v>0.124437781109445</v>
       </c>
     </row>
     <row r="66">
@@ -4738,7 +4738,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
@@ -4747,22 +4747,22 @@
         <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>0.892053973013493</v>
+        <v>0.28309325502308</v>
       </c>
       <c r="M66" t="n">
-        <v>0.187406296851574</v>
+        <v>0.450274862568716</v>
       </c>
       <c r="N66" t="n">
-        <v>0.11544227886057</v>
+        <v>0.784107946026987</v>
       </c>
       <c r="O66" t="n">
-        <v>0.192903548225887</v>
+        <v>0.633183408295852</v>
       </c>
       <c r="P66" t="n">
-        <v>0.579603626629426</v>
+        <v>0.156921539230385</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.178910544727636</v>
+        <v>0.679160419790105</v>
       </c>
     </row>
     <row r="67">
@@ -4788,34 +4788,34 @@
         <v>0.684210526315789</v>
       </c>
       <c r="H67" t="n">
-        <v>0.96892003547262</v>
+        <v>0.268283144867637</v>
       </c>
       <c r="I67" t="n">
-        <v>0.967911385386393</v>
+        <v>0.740870018549792</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0.430666843426739</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0.359943475692557</v>
       </c>
       <c r="L67" t="n">
-        <v>0.377811094452774</v>
+        <v>0.886018422162724</v>
       </c>
       <c r="M67" t="n">
-        <v>0.707646176911544</v>
+        <v>0.557721139430285</v>
       </c>
       <c r="N67" t="n">
-        <v>0.776611694152924</v>
+        <v>0.197401299350325</v>
       </c>
       <c r="O67" t="n">
-        <v>0.116941529235382</v>
+        <v>0.264367816091954</v>
       </c>
       <c r="P67" t="n">
-        <v>0.726527126840092</v>
+        <v>0.263868065967017</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.800099950024987</v>
+        <v>0.32183908045977</v>
       </c>
     </row>
     <row r="68">
@@ -4841,34 +4841,34 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>0.592783601954566</v>
+        <v>0.67463203654944</v>
       </c>
       <c r="I68" t="n">
-        <v>0.651712185877717</v>
+        <v>0.829723186836647</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0.397515631749189</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0.484757621189405</v>
+        <v>0.486286777422666</v>
       </c>
       <c r="M68" t="n">
-        <v>0.424287856071964</v>
+        <v>0.5952023988006</v>
       </c>
       <c r="N68" t="n">
-        <v>0.619690154922539</v>
+        <v>0.511244377811094</v>
       </c>
       <c r="O68" t="n">
-        <v>0.55272363818091</v>
+        <v>0.663168415792104</v>
       </c>
       <c r="P68" t="n">
-        <v>0.823513108452599</v>
+        <v>0.590704647676162</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.56071964017991</v>
+        <v>0.569215392303848</v>
       </c>
     </row>
     <row r="69">
@@ -4894,34 +4894,34 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I69" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>0.571714142928536</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>0.520739630184908</v>
+        <v>0.545227386306847</v>
       </c>
       <c r="N69" t="n">
-        <v>0.519740129935032</v>
+        <v>0.438280859570215</v>
       </c>
       <c r="O69" t="n">
-        <v>0.277861069465267</v>
+        <v>0.609195402298851</v>
       </c>
       <c r="P69" t="n">
-        <v>1</v>
+        <v>0.815092453773113</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.544727636181909</v>
+        <v>0.561219390304848</v>
       </c>
     </row>
     <row r="70">
@@ -4947,34 +4947,34 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I70" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J70" t="n">
-        <v>0.225577437233472</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K70" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0.878060969515242</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0.116441779110445</v>
+        <v>0.590704647676162</v>
       </c>
       <c r="N70" t="n">
-        <v>0.111444277861069</v>
+        <v>0.493253373313343</v>
       </c>
       <c r="O70" t="n">
-        <v>0.703148425787106</v>
+        <v>0.711644177911045</v>
       </c>
       <c r="P70" t="n">
-        <v>0.123411126417398</v>
+        <v>0.934032983508246</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.0979510244877561</v>
+        <v>0.618190904547726</v>
       </c>
     </row>
     <row r="71">
@@ -5000,34 +5000,34 @@
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I71" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J71" t="n">
-        <v>0.225577437233472</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K71" t="n">
-        <v>0.225577437233472</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>0.672663668165917</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0.421289355322339</v>
+        <v>0.217891054472764</v>
       </c>
       <c r="N71" t="n">
-        <v>0.228885557221389</v>
+        <v>0.677161419290355</v>
       </c>
       <c r="O71" t="n">
-        <v>0.242378810594703</v>
+        <v>0.866066966516742</v>
       </c>
       <c r="P71" t="n">
-        <v>0.579603626629426</v>
+        <v>0.754122938530735</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.460269865067466</v>
+        <v>0.772613693153423</v>
       </c>
     </row>
     <row r="72">
@@ -5053,34 +5053,34 @@
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0.686586889163176</v>
+        <v>0.741426031795175</v>
       </c>
       <c r="I72" t="n">
-        <v>0.40961216539683</v>
+        <v>0.587058785749398</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0.548253916758134</v>
       </c>
       <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>0.463268365817091</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>0.665167416291854</v>
+        <v>0.174912543728136</v>
       </c>
       <c r="N72" t="n">
-        <v>0.754622688655672</v>
+        <v>0.31384307846077</v>
       </c>
       <c r="O72" t="n">
-        <v>0.512743628185907</v>
+        <v>0.656671664167916</v>
       </c>
       <c r="P72" t="n">
-        <v>0.579603626629426</v>
+        <v>0.683158420789605</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.794602698650675</v>
+        <v>0.480259870064968</v>
       </c>
     </row>
   </sheetData>

--- a/data/complex_df_with_p_values.xlsx
+++ b/data/complex_df_with_p_values.xlsx
@@ -1343,34 +1343,34 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I2" t="n">
-        <v>0.587058785749398</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M2" t="n">
-        <v>0.142928535732134</v>
+        <v>0.802098950524738</v>
       </c>
       <c r="N2" t="n">
-        <v>0.692153923038481</v>
+        <v>0.461769115442279</v>
       </c>
       <c r="O2" t="n">
-        <v>0.869065467266367</v>
+        <v>0.240379810094953</v>
       </c>
       <c r="P2" t="n">
-        <v>0.614692653673163</v>
+        <v>0.293853073463268</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.771114442778611</v>
+        <v>0.438280859570215</v>
       </c>
     </row>
     <row r="3">
@@ -1396,34 +1396,34 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I3" t="n">
-        <v>0.587058785749398</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.300466626758702</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M3" t="n">
-        <v>0.276361819090455</v>
+        <v>0.818090954522739</v>
       </c>
       <c r="N3" t="n">
-        <v>0.67216391804098</v>
+        <v>0.363318340829585</v>
       </c>
       <c r="O3" t="n">
-        <v>0.315342328835582</v>
+        <v>0.181409295352324</v>
       </c>
       <c r="P3" t="n">
-        <v>0.375312343828086</v>
+        <v>0.497751124437781</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.505747126436782</v>
+        <v>0.231884057971014</v>
       </c>
     </row>
     <row r="4">
@@ -1449,34 +1449,34 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I4" t="n">
-        <v>0.587058785749398</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J4" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.262368815592204</v>
+        <v>0.36631684157921</v>
       </c>
       <c r="N4" t="n">
-        <v>0.72263868065967</v>
+        <v>0.384807596201899</v>
       </c>
       <c r="O4" t="n">
-        <v>0.829585207396302</v>
+        <v>0.648675662168916</v>
       </c>
       <c r="P4" t="n">
-        <v>0.414292853573213</v>
+        <v>0.794102948525737</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.800599700149925</v>
+        <v>0.469765117441279</v>
       </c>
     </row>
     <row r="5">
@@ -1502,22 +1502,22 @@
         <v>0.5625</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0016293116063111</v>
+        <v>0.00520698578866087</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.335790249468997</v>
+        <v>0.794688452540781</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00805470289817191</v>
+        <v>0.00186061129655719</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0.99800099950025</v>
       </c>
       <c r="N5" t="n">
         <v>0.000499750124937531</v>
@@ -1526,10 +1526,10 @@
         <v>0.000499750124937531</v>
       </c>
       <c r="P5" t="n">
-        <v>0.35832083958021</v>
+        <v>0.377811094452774</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.00149925037481259</v>
       </c>
     </row>
     <row r="6">
@@ -1555,34 +1555,34 @@
         <v>0.5625</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0016293116063111</v>
+        <v>0.00520698578866087</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0.335790249468997</v>
+        <v>0.794688452540781</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00805470289817191</v>
+        <v>0.00186061129655719</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.997501249375312</v>
       </c>
       <c r="N6" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
       <c r="O6" t="n">
         <v>0.000499750124937531</v>
       </c>
       <c r="P6" t="n">
-        <v>0.363318340829585</v>
+        <v>0.374312843578211</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.000499750124937531</v>
+        <v>0.000999500249875062</v>
       </c>
     </row>
     <row r="7">
@@ -1608,34 +1608,34 @@
         <v>0.75</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.914263231619332</v>
       </c>
       <c r="I7" t="n">
-        <v>0.734784062780603</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.602029078104202</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0630802617661833</v>
+        <v>0.145949859984731</v>
       </c>
       <c r="M7" t="n">
-        <v>0.144427786106947</v>
+        <v>0.621189405297351</v>
       </c>
       <c r="N7" t="n">
-        <v>0.949525237381309</v>
+        <v>0.825087456271864</v>
       </c>
       <c r="O7" t="n">
-        <v>0.695652173913043</v>
+        <v>0.297351324337831</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0559720139930035</v>
+        <v>0.0574712643678161</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.861569215392304</v>
+        <v>0.56271864067966</v>
       </c>
     </row>
     <row r="8">
@@ -1661,34 +1661,34 @@
         <v>0.75</v>
       </c>
       <c r="H8" t="n">
-        <v>0.487003861409952</v>
+        <v>0.914263231619332</v>
       </c>
       <c r="I8" t="n">
-        <v>0.734784062780603</v>
+        <v>0.503129728765281</v>
       </c>
       <c r="J8" t="n">
-        <v>0.251732081772143</v>
+        <v>0.649013399712091</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.562857661905461</v>
       </c>
       <c r="M8" t="n">
-        <v>0.680659670164918</v>
+        <v>0.173913043478261</v>
       </c>
       <c r="N8" t="n">
-        <v>0.314342828585707</v>
+        <v>0.488255872063968</v>
       </c>
       <c r="O8" t="n">
-        <v>0.699150424787606</v>
+        <v>0.924037981009495</v>
       </c>
       <c r="P8" t="n">
-        <v>0.964017991004498</v>
+        <v>0.268365817091454</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.471764117941029</v>
+        <v>0.729135432283858</v>
       </c>
     </row>
     <row r="9">
@@ -1714,7 +1714,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.241255174106044</v>
+        <v>0.311977906248122</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1723,25 +1723,25 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0.026666150662722</v>
+        <v>0.0697148776288411</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0.926536731634183</v>
+        <v>0.813593203398301</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0424787606196902</v>
+        <v>0.156421789105447</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0109945027486257</v>
+        <v>0.0594702648675662</v>
       </c>
       <c r="P9" t="n">
-        <v>0.264367816091954</v>
+        <v>0.184407796101949</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0434782608695652</v>
+        <v>0.185407296351824</v>
       </c>
     </row>
     <row r="10">
@@ -1767,13 +1767,13 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H10" t="n">
-        <v>0.241255174106044</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J10" t="n">
-        <v>0.107294511721661</v>
+        <v>0.502289493034358</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -1782,19 +1782,19 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0.706146926536732</v>
+        <v>0.0844577711144428</v>
       </c>
       <c r="N10" t="n">
-        <v>0.330834582708646</v>
+        <v>0.619190404797601</v>
       </c>
       <c r="O10" t="n">
-        <v>0.664667666166917</v>
+        <v>0.989005497251374</v>
       </c>
       <c r="P10" t="n">
-        <v>0.991004497751124</v>
+        <v>0.686656671664168</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.482758620689655</v>
+        <v>0.822588705647176</v>
       </c>
     </row>
     <row r="11">
@@ -1823,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.127501830029947</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1832,22 +1832,22 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0.0579117377641227</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00699650174912544</v>
+        <v>0.0519740129935032</v>
       </c>
       <c r="N11" t="n">
-        <v>0.989005497251374</v>
+        <v>0.980509745127436</v>
       </c>
       <c r="O11" t="n">
-        <v>0.909045477261369</v>
+        <v>0.893553223388306</v>
       </c>
       <c r="P11" t="n">
-        <v>0.190404797601199</v>
+        <v>0.0189905047476262</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.995002498750625</v>
+        <v>0.96551724137931</v>
       </c>
     </row>
     <row r="12">
@@ -1876,7 +1876,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.127501830029947</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1885,22 +1885,22 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0619690154922539</v>
+        <v>0.0299850074962519</v>
       </c>
       <c r="N12" t="n">
-        <v>0.881559220389805</v>
+        <v>0.982008995502249</v>
       </c>
       <c r="O12" t="n">
-        <v>0.910544727636182</v>
+        <v>0.931534232883558</v>
       </c>
       <c r="P12" t="n">
-        <v>0.397801099450275</v>
+        <v>0.0659670164917541</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.925537231384308</v>
+        <v>0.986506746626687</v>
       </c>
     </row>
     <row r="13">
@@ -1926,13 +1926,13 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.241255174106044</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.0430857804408705</v>
       </c>
       <c r="J13" t="n">
-        <v>0.107294511721661</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -1941,19 +1941,19 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.623188405797101</v>
+        <v>0.222888555722139</v>
       </c>
       <c r="N13" t="n">
-        <v>0.489255372313843</v>
+        <v>0.68415792103948</v>
       </c>
       <c r="O13" t="n">
-        <v>0.746626686656672</v>
+        <v>0.974012993503248</v>
       </c>
       <c r="P13" t="n">
-        <v>0.972513743128436</v>
+        <v>0.903048475762119</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.623188405797101</v>
+        <v>0.863568215892054</v>
       </c>
     </row>
     <row r="14">
@@ -1979,34 +1979,34 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I14" t="n">
-        <v>0.587058785749398</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L14" t="n">
-        <v>0.28309325502308</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3928035982009</v>
+        <v>0.382308845577211</v>
       </c>
       <c r="N14" t="n">
-        <v>0.79960019990005</v>
+        <v>0.545227386306847</v>
       </c>
       <c r="O14" t="n">
-        <v>0.747126436781609</v>
+        <v>0.487756121939031</v>
       </c>
       <c r="P14" t="n">
-        <v>0.160419790104948</v>
+        <v>0.727636181909045</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.813593203398301</v>
+        <v>0.504747626186906</v>
       </c>
     </row>
     <row r="15">
@@ -2032,34 +2032,34 @@
         <v>0.833333333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>0.48374600885126</v>
+        <v>0.87768997533825</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0.27870827146302</v>
       </c>
       <c r="J15" t="n">
-        <v>0.863159620211482</v>
+        <v>0.825591465723243</v>
       </c>
       <c r="K15" t="n">
-        <v>0.19007397503006</v>
+        <v>0.784928130624501</v>
       </c>
       <c r="L15" t="n">
-        <v>0.170567192713679</v>
+        <v>0.748475362475682</v>
       </c>
       <c r="M15" t="n">
-        <v>0.907046476761619</v>
+        <v>0.0844577711144428</v>
       </c>
       <c r="N15" t="n">
-        <v>0.352823588205897</v>
+        <v>0.898550724637681</v>
       </c>
       <c r="O15" t="n">
-        <v>0.130934532733633</v>
+        <v>0.865067466266867</v>
       </c>
       <c r="P15" t="n">
-        <v>0.00599700149925037</v>
+        <v>0.184407796101949</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.167416291854073</v>
+        <v>0.948025987006497</v>
       </c>
     </row>
     <row r="16">
@@ -2085,34 +2085,34 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.241255174106044</v>
+        <v>0.311977906248122</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.107294511721661</v>
+        <v>0.502289493034358</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>0.893553223388306</v>
+        <v>0.822088955522239</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0484757621189405</v>
+        <v>0.227386306846577</v>
       </c>
       <c r="O16" t="n">
-        <v>0.237881059470265</v>
+        <v>0.222888555722139</v>
       </c>
       <c r="P16" t="n">
-        <v>0.902048975512244</v>
+        <v>0.713143428285857</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.112443778110945</v>
+        <v>0.183908045977011</v>
       </c>
     </row>
     <row r="17">
@@ -2138,34 +2138,34 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I17" t="n">
-        <v>0.587058785749398</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J17" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0.443778110944528</v>
+        <v>0.478760619690155</v>
       </c>
       <c r="N17" t="n">
-        <v>0.211394302848576</v>
+        <v>0.32383808095952</v>
       </c>
       <c r="O17" t="n">
-        <v>0.451774112943528</v>
+        <v>0.308845577211394</v>
       </c>
       <c r="P17" t="n">
-        <v>0.72663668165917</v>
+        <v>0.742628685657171</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.346326836581709</v>
+        <v>0.308845577211394</v>
       </c>
     </row>
     <row r="18">
@@ -2191,13 +2191,13 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H18" t="n">
-        <v>0.299375686270464</v>
+        <v>0.770284969550768</v>
       </c>
       <c r="I18" t="n">
-        <v>0.829723186836647</v>
+        <v>0.19274547192714</v>
       </c>
       <c r="J18" t="n">
-        <v>0.105948531795098</v>
+        <v>0.338403792644963</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -2206,19 +2206,19 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0.903048475762119</v>
+        <v>0.16191904047976</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0379810094952524</v>
+        <v>0.424287856071964</v>
       </c>
       <c r="O18" t="n">
-        <v>0.273863068465767</v>
+        <v>0.593703148425787</v>
       </c>
       <c r="P18" t="n">
-        <v>0.949025487256372</v>
+        <v>0.626186906546727</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.103948025987006</v>
+        <v>0.618190904547726</v>
       </c>
     </row>
     <row r="19">
@@ -2244,34 +2244,34 @@
         <v>0.75</v>
       </c>
       <c r="H19" t="n">
-        <v>0.868637116987786</v>
+        <v>0.587688631358857</v>
       </c>
       <c r="I19" t="n">
-        <v>0.291608231686989</v>
+        <v>0.503129728765281</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0.415033749543885</v>
+        <v>0.17242902617127</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>0.397301349325337</v>
+        <v>0.486256871564218</v>
       </c>
       <c r="N19" t="n">
-        <v>0.47976011994003</v>
+        <v>0.56271864067966</v>
       </c>
       <c r="O19" t="n">
-        <v>0.399800099950025</v>
+        <v>0.419790104947526</v>
       </c>
       <c r="P19" t="n">
-        <v>0.347826086956522</v>
+        <v>0.35632183908046</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.55672163918041</v>
+        <v>0.568215892053973</v>
       </c>
     </row>
     <row r="20">
@@ -2297,34 +2297,34 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.241255174106044</v>
+        <v>0.311977906248122</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.548253916758134</v>
+        <v>0.502289493034358</v>
       </c>
       <c r="K20" t="n">
-        <v>0.300466626758702</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0.924037981009495</v>
+        <v>0.933533233383308</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0559720139930035</v>
+        <v>0.140429785107446</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0834582708645677</v>
+        <v>0.105947026486757</v>
       </c>
       <c r="P20" t="n">
-        <v>0.71264367816092</v>
+        <v>0.578710644677661</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.071464267866067</v>
+        <v>0.0969515242378811</v>
       </c>
     </row>
     <row r="21">
@@ -2350,7 +2350,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0.300466626758702</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L21" t="n">
-        <v>0.28309325502308</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M21" t="n">
+        <v>0.399800099950025</v>
+      </c>
+      <c r="N21" t="n">
         <v>0.776611694152924</v>
       </c>
-      <c r="N21" t="n">
-        <v>0.359320339830085</v>
-      </c>
       <c r="O21" t="n">
-        <v>0.0939530234882559</v>
+        <v>0.509245377311344</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0599700149925037</v>
+        <v>0.149425287356322</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.205897051474263</v>
+        <v>0.725137431284358</v>
       </c>
     </row>
     <row r="22">
@@ -2403,34 +2403,34 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.741426031795175</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.28309325502308</v>
+        <v>0.0579117377641227</v>
       </c>
       <c r="M22" t="n">
-        <v>0.763618190904548</v>
+        <v>0.316841579210395</v>
       </c>
       <c r="N22" t="n">
-        <v>0.280359820089955</v>
+        <v>0.914542728635682</v>
       </c>
       <c r="O22" t="n">
-        <v>0.171914042978511</v>
+        <v>0.619690154922539</v>
       </c>
       <c r="P22" t="n">
-        <v>0.0934532733633183</v>
+        <v>0.108945527236382</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.219390304847576</v>
+        <v>0.806096951524238</v>
       </c>
     </row>
     <row r="23">
@@ -2456,34 +2456,34 @@
         <v>0.75</v>
       </c>
       <c r="H23" t="n">
-        <v>0.868637116987786</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.291608231686989</v>
+        <v>0.503129728765281</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0.415033749543885</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0.145949859984731</v>
       </c>
       <c r="M23" t="n">
-        <v>0.27936031984008</v>
+        <v>0.0214892553723138</v>
       </c>
       <c r="N23" t="n">
-        <v>0.761619190404798</v>
+        <v>0.9960019990005</v>
       </c>
       <c r="O23" t="n">
-        <v>0.574712643678161</v>
+        <v>0.958020989505247</v>
       </c>
       <c r="P23" t="n">
-        <v>0.536231884057971</v>
+        <v>0.0449775112443778</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.702648675662169</v>
+        <v>0.993003498250875</v>
       </c>
     </row>
     <row r="24">
@@ -2509,7 +2509,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.241255174106044</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -2518,25 +2518,25 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0.026666150662722</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0.0579117377641227</v>
       </c>
       <c r="M24" t="n">
-        <v>0.916041979010495</v>
+        <v>0.659670164917541</v>
       </c>
       <c r="N24" t="n">
-        <v>0.139430284857571</v>
+        <v>0.612193903048476</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0109945027486257</v>
+        <v>0.272363818090955</v>
       </c>
       <c r="P24" t="n">
-        <v>0.240379810094953</v>
+        <v>0.0619690154922539</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0719640179910045</v>
+        <v>0.455772113943028</v>
       </c>
     </row>
     <row r="25">
@@ -2562,34 +2562,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H25" t="n">
-        <v>0.741426031795175</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0.587058785749398</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J25" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M25" t="n">
-        <v>0.144927536231884</v>
+        <v>0.0949525237381309</v>
       </c>
       <c r="N25" t="n">
-        <v>0.756121939030485</v>
+        <v>0.864067966016992</v>
       </c>
       <c r="O25" t="n">
-        <v>0.900549725137431</v>
+        <v>0.847576211894053</v>
       </c>
       <c r="P25" t="n">
-        <v>0.671164417791104</v>
+        <v>0.166416791604198</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.833583208395802</v>
+        <v>0.877061469265367</v>
       </c>
     </row>
     <row r="26">
@@ -2615,34 +2615,34 @@
         <v>0.75</v>
       </c>
       <c r="H26" t="n">
-        <v>0.487003861409952</v>
+        <v>0.914263231619332</v>
       </c>
       <c r="I26" t="n">
-        <v>0.734784062780603</v>
+        <v>0.503129728765281</v>
       </c>
       <c r="J26" t="n">
-        <v>0.696514834251129</v>
+        <v>0.649013399712091</v>
       </c>
       <c r="K26" t="n">
-        <v>0.415033749543885</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0.562857661905461</v>
       </c>
       <c r="M26" t="n">
-        <v>0.533733133433283</v>
+        <v>0.283858070964518</v>
       </c>
       <c r="N26" t="n">
-        <v>0.567216391804098</v>
+        <v>0.534732633683158</v>
       </c>
       <c r="O26" t="n">
-        <v>0.408795602198901</v>
+        <v>0.830084957521239</v>
       </c>
       <c r="P26" t="n">
-        <v>0.768615692153923</v>
+        <v>0.657171414292854</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.455272363818091</v>
+        <v>0.707146426786607</v>
       </c>
     </row>
     <row r="27">
@@ -2668,34 +2668,34 @@
         <v>0.8</v>
       </c>
       <c r="H27" t="n">
-        <v>0.299375686270464</v>
+        <v>0.405092293166947</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.606591147711328</v>
       </c>
       <c r="J27" t="n">
-        <v>0.105948531795098</v>
+        <v>0.0792795667128238</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0.486286777422666</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0.84407796101949</v>
+        <v>0.71264367816092</v>
       </c>
       <c r="N27" t="n">
-        <v>0.162418790604698</v>
+        <v>0.0489755122438781</v>
       </c>
       <c r="O27" t="n">
-        <v>0.227386306846577</v>
+        <v>0.402298850574713</v>
       </c>
       <c r="P27" t="n">
-        <v>0.657671164417791</v>
+        <v>0.936531734132934</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.223388305847076</v>
+        <v>0.239380309845077</v>
       </c>
     </row>
     <row r="28">
@@ -2721,13 +2721,13 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.241255174106044</v>
+        <v>0.311977906248122</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.107294511721661</v>
+        <v>0.0865495063242047</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -2736,19 +2736,19 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0.903048475762119</v>
+        <v>0.977511244377811</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0719640179910045</v>
+        <v>0.0129935032483758</v>
       </c>
       <c r="O28" t="n">
-        <v>0.28735632183908</v>
+        <v>0.211394302848576</v>
       </c>
       <c r="P28" t="n">
-        <v>0.929535232383808</v>
+        <v>0.84007996001999</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.137431284357821</v>
+        <v>0.00449775112443778</v>
       </c>
     </row>
     <row r="29">
@@ -2774,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.241255174106044</v>
+        <v>0.311977906248122</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.107294511721661</v>
+        <v>0.0865495063242047</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -2789,19 +2789,19 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0.989005497251374</v>
+        <v>0.993003498250875</v>
       </c>
       <c r="N29" t="n">
-        <v>0.0304847576211894</v>
+        <v>0.0109945027486257</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0934532733633183</v>
+        <v>0.111444277861069</v>
       </c>
       <c r="P29" t="n">
-        <v>0.804597701149425</v>
+        <v>0.767616191904048</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0904547726136932</v>
+        <v>0.0809595202398801</v>
       </c>
     </row>
     <row r="30">
@@ -2827,34 +2827,34 @@
         <v>0.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0.933305477133902</v>
+        <v>0.0971326272013562</v>
       </c>
       <c r="I30" t="n">
-        <v>0.133249772761508</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.796181235085109</v>
+        <v>0.752549935401133</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0.0589549764640494</v>
       </c>
       <c r="L30" t="n">
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>0.143428285857071</v>
+        <v>0.989005497251374</v>
       </c>
       <c r="N30" t="n">
-        <v>0.685657171414293</v>
+        <v>0.0794602698650675</v>
       </c>
       <c r="O30" t="n">
-        <v>0.934532733633183</v>
+        <v>0.024487756121939</v>
       </c>
       <c r="P30" t="n">
-        <v>0.819590204897551</v>
+        <v>0.702148925537231</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.823088455772114</v>
+        <v>0.0379810094952524</v>
       </c>
     </row>
     <row r="31">
@@ -2880,34 +2880,34 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.11838083045409</v>
+        <v>0.914263231619332</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0.503129728765281</v>
       </c>
       <c r="J31" t="n">
-        <v>0.696514834251129</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0713323811883347</v>
+        <v>0.602029078104202</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0.562857661905461</v>
       </c>
       <c r="M31" t="n">
-        <v>0.965017491254373</v>
+        <v>0.292853573213393</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0864567716141929</v>
+        <v>0.908045977011494</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0204897551224388</v>
+        <v>0.47976011994003</v>
       </c>
       <c r="P31" t="n">
-        <v>0.407796101949025</v>
+        <v>0.0774612693653173</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0334832583708146</v>
+        <v>0.723138430784608</v>
       </c>
     </row>
     <row r="32">
@@ -2933,34 +2933,34 @@
         <v>0.6</v>
       </c>
       <c r="H32" t="n">
-        <v>0.487003861409952</v>
+        <v>0.174122543692754</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0.251732081772143</v>
+        <v>0.208841679678894</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0.602029078104202</v>
       </c>
       <c r="L32" t="n">
-        <v>0.393099751651528</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>0.800099950024987</v>
+        <v>0.96751624187906</v>
       </c>
       <c r="N32" t="n">
-        <v>0.221889055472264</v>
+        <v>0.095952023988006</v>
       </c>
       <c r="O32" t="n">
-        <v>0.257371314342829</v>
+        <v>0.0849575212393803</v>
       </c>
       <c r="P32" t="n">
-        <v>0.365317341329335</v>
+        <v>0.709145427286357</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.290354822588706</v>
+        <v>0.104447776111944</v>
       </c>
     </row>
     <row r="33">
@@ -2986,34 +2986,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H33" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I33" t="n">
-        <v>0.587058785749398</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.300466626758702</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M33" t="n">
-        <v>0.329335332333833</v>
+        <v>0.415792103948026</v>
       </c>
       <c r="N33" t="n">
-        <v>0.381309345327336</v>
+        <v>0.550224887556222</v>
       </c>
       <c r="O33" t="n">
-        <v>0.284857571214393</v>
+        <v>0.336331834082959</v>
       </c>
       <c r="P33" t="n">
-        <v>0.354822588705647</v>
+        <v>0.111444277861069</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.448275862068966</v>
+        <v>0.569715142428786</v>
       </c>
     </row>
     <row r="34">
@@ -3039,34 +3039,34 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.868637116987786</v>
+        <v>0.914263231619332</v>
       </c>
       <c r="I34" t="n">
-        <v>0.291608231686989</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0.415033749543885</v>
+        <v>0.602029078104202</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0.145949859984731</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0809595202398801</v>
+        <v>0.278360819590205</v>
       </c>
       <c r="N34" t="n">
-        <v>0.64767616191904</v>
+        <v>0.782608695652174</v>
       </c>
       <c r="O34" t="n">
-        <v>0.509745127436282</v>
+        <v>0.515242378810595</v>
       </c>
       <c r="P34" t="n">
-        <v>0.269865067466267</v>
+        <v>0.0219890054972514</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.742628685657171</v>
+        <v>0.770614692653673</v>
       </c>
     </row>
     <row r="35">
@@ -3092,34 +3092,34 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.868637116987786</v>
+        <v>0.914263231619332</v>
       </c>
       <c r="I35" t="n">
-        <v>0.291608231686989</v>
+        <v>0.503129728765281</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0.415033749543885</v>
+        <v>0.602029078104202</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0.562857661905461</v>
       </c>
       <c r="M35" t="n">
-        <v>0.215892053973014</v>
+        <v>0.20439780109945</v>
       </c>
       <c r="N35" t="n">
-        <v>0.506746626686657</v>
+        <v>0.780109945027486</v>
       </c>
       <c r="O35" t="n">
-        <v>0.488755622188906</v>
+        <v>0.59720139930035</v>
       </c>
       <c r="P35" t="n">
-        <v>0.484257871064468</v>
+        <v>0.0399800099950025</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.612693653173413</v>
+        <v>0.818090954522739</v>
       </c>
     </row>
     <row r="36">
@@ -3145,34 +3145,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H36" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I36" t="n">
-        <v>0.587058785749398</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.300466626758702</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0.60119940029985</v>
+        <v>0.305847076461769</v>
       </c>
       <c r="N36" t="n">
-        <v>0.24287856071964</v>
+        <v>0.569715142428786</v>
       </c>
       <c r="O36" t="n">
-        <v>0.286356821589205</v>
+        <v>0.431784107946027</v>
       </c>
       <c r="P36" t="n">
-        <v>0.605697151424288</v>
+        <v>0.215392303848076</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.323338330834583</v>
+        <v>0.671164417791104</v>
       </c>
     </row>
     <row r="37">
@@ -3198,34 +3198,34 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.741426031795175</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.587058785749398</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J37" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M37" t="n">
-        <v>0.273863068465767</v>
+        <v>0.138930534732634</v>
       </c>
       <c r="N37" t="n">
-        <v>0.5952023988006</v>
+        <v>0.990004997501249</v>
       </c>
       <c r="O37" t="n">
-        <v>0.694152923538231</v>
+        <v>0.600699650174913</v>
       </c>
       <c r="P37" t="n">
-        <v>0.431284357821089</v>
+        <v>0.224387806096952</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.658670664667666</v>
+        <v>0.795102448775612</v>
       </c>
     </row>
     <row r="38">
@@ -3251,13 +3251,13 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.741426031795175</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.587058785749398</v>
+        <v>0.0430857804408705</v>
       </c>
       <c r="J38" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -3266,19 +3266,19 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>0.529735132433783</v>
+        <v>0.023488255872064</v>
       </c>
       <c r="N38" t="n">
-        <v>0.440279860069965</v>
+        <v>0.992503748125937</v>
       </c>
       <c r="O38" t="n">
-        <v>0.731134432783608</v>
+        <v>0.792603698150925</v>
       </c>
       <c r="P38" t="n">
-        <v>0.893053473263368</v>
+        <v>0.604697651174413</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.578210894552724</v>
+        <v>0.887056471764118</v>
       </c>
     </row>
     <row r="39">
@@ -3304,34 +3304,34 @@
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.741426031795175</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0.587058785749398</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J39" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M39" t="n">
-        <v>0.472763618190905</v>
+        <v>0.347826086956522</v>
       </c>
       <c r="N39" t="n">
-        <v>0.44727636181909</v>
+        <v>0.901049475262369</v>
       </c>
       <c r="O39" t="n">
-        <v>0.768115942028985</v>
+        <v>0.3928035982009</v>
       </c>
       <c r="P39" t="n">
-        <v>0.877061469265367</v>
+        <v>0.470264867566217</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.590204897551224</v>
+        <v>0.638680659670165</v>
       </c>
     </row>
     <row r="40">
@@ -3357,34 +3357,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>0.241255174106044</v>
+        <v>0.311977906248122</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.300466626758702</v>
+        <v>0.0697148776288411</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0.95552223888056</v>
+        <v>0.900049975012494</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0129935032483758</v>
+        <v>0.0644677661169415</v>
       </c>
       <c r="O40" t="n">
-        <v>0.00549725137431284</v>
+        <v>0.0164917541229385</v>
       </c>
       <c r="P40" t="n">
-        <v>0.380809595202399</v>
+        <v>0.372813593203398</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.024487756121939</v>
+        <v>0.0964517741129435</v>
       </c>
     </row>
     <row r="41">
@@ -3410,34 +3410,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H41" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I41" t="n">
-        <v>0.587058785749398</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J41" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0.72263868065967</v>
+        <v>0.429285357321339</v>
       </c>
       <c r="N41" t="n">
-        <v>0.19240379810095</v>
+        <v>0.670664667666167</v>
       </c>
       <c r="O41" t="n">
-        <v>0.47376311844078</v>
+        <v>0.488755622188906</v>
       </c>
       <c r="P41" t="n">
-        <v>0.87856071964018</v>
+        <v>0.618690654672664</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.286356821589205</v>
+        <v>0.554222888555722</v>
       </c>
     </row>
     <row r="42">
@@ -3463,34 +3463,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H42" t="n">
-        <v>0.241255174106044</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I42" t="n">
-        <v>0.587058785749398</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J42" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0.300466626758702</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>0.424787606196902</v>
+        <v>0.998500749625187</v>
       </c>
       <c r="O42" t="n">
-        <v>0.501749125437281</v>
+        <v>0.809595202398801</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>0.816591704147926</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.307346326836582</v>
+        <v>0.84207896051974</v>
       </c>
     </row>
     <row r="43">
@@ -3516,34 +3516,34 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0.868637116987786</v>
+        <v>0.587688631358857</v>
       </c>
       <c r="I43" t="n">
-        <v>0.291608231686989</v>
+        <v>0.503129728765281</v>
       </c>
       <c r="J43" t="n">
-        <v>0.696514834251129</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0.17242902617127</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>0.341829085457271</v>
+        <v>0.572713643178411</v>
       </c>
       <c r="N43" t="n">
-        <v>0.420289855072464</v>
+        <v>0.714142928535732</v>
       </c>
       <c r="O43" t="n">
-        <v>0.715642178910545</v>
+        <v>0.360819590204898</v>
       </c>
       <c r="P43" t="n">
-        <v>0.790104947526237</v>
+        <v>0.465767116441779</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.584707646176912</v>
+        <v>0.515742128935532</v>
       </c>
     </row>
     <row r="44">
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -3581,22 +3581,22 @@
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.0234002514704269</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M44" t="n">
-        <v>0.52423788105947</v>
+        <v>0.0264867566216892</v>
       </c>
       <c r="N44" t="n">
-        <v>0.835582208895552</v>
+        <v>0.978010994502749</v>
       </c>
       <c r="O44" t="n">
-        <v>0.386306846576712</v>
+        <v>0.929535232383808</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0199900049975013</v>
+        <v>0.20439780109945</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.614192903548226</v>
+        <v>0.977011494252874</v>
       </c>
     </row>
     <row r="45">
@@ -3634,22 +3634,22 @@
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.0234002514704269</v>
+        <v>0.0579117377641227</v>
       </c>
       <c r="M45" t="n">
-        <v>0.376311844077961</v>
+        <v>0.272863568215892</v>
       </c>
       <c r="N45" t="n">
-        <v>0.818590704647676</v>
+        <v>0.95352323838081</v>
       </c>
       <c r="O45" t="n">
-        <v>0.43528235882059</v>
+        <v>0.712143928035982</v>
       </c>
       <c r="P45" t="n">
-        <v>0.0264867566216892</v>
+        <v>0.0444777611194403</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.676661669165417</v>
+        <v>0.864567716141929</v>
       </c>
     </row>
     <row r="46">
@@ -3678,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0.734784062780603</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -3687,22 +3687,22 @@
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0.0630802617661833</v>
+        <v>0.0138926766538187</v>
       </c>
       <c r="M46" t="n">
-        <v>0.156921539230385</v>
+        <v>0.111444277861069</v>
       </c>
       <c r="N46" t="n">
-        <v>0.92103948025987</v>
+        <v>0.989005497251374</v>
       </c>
       <c r="O46" t="n">
-        <v>0.68815592203898</v>
+        <v>0.862568715642179</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0514742628685657</v>
+        <v>0.0229885057471264</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.857571214392804</v>
+        <v>0.95952023988006</v>
       </c>
     </row>
     <row r="47">
@@ -3731,7 +3731,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.127501830029947</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -3740,22 +3740,22 @@
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0.0579117377641227</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0754622688655672</v>
+        <v>0.268365817091454</v>
       </c>
       <c r="N47" t="n">
-        <v>0.855072463768116</v>
+        <v>0.902048975512244</v>
       </c>
       <c r="O47" t="n">
-        <v>0.971014492753623</v>
+        <v>0.75712143928036</v>
       </c>
       <c r="P47" t="n">
-        <v>0.568215892053973</v>
+        <v>0.0444777611194403</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.926536731634183</v>
+        <v>0.890054972513743</v>
       </c>
     </row>
     <row r="48">
@@ -3784,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.127501830029947</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -3793,22 +3793,22 @@
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M48" t="n">
-        <v>0.133433283358321</v>
+        <v>0.0204897551224388</v>
       </c>
       <c r="N48" t="n">
-        <v>0.805097451274363</v>
+        <v>0.976511744127936</v>
       </c>
       <c r="O48" t="n">
-        <v>0.923538230884558</v>
+        <v>0.966016991504248</v>
       </c>
       <c r="P48" t="n">
-        <v>0.642178910544728</v>
+        <v>0.106446776611694</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.879060469765117</v>
+        <v>0.987006496751624</v>
       </c>
     </row>
     <row r="49">
@@ -3834,34 +3834,34 @@
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I49" t="n">
-        <v>0.127501830029947</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M49" t="n">
-        <v>0.0424787606196902</v>
+        <v>0.709145427286357</v>
       </c>
       <c r="N49" t="n">
-        <v>0.87256371814093</v>
+        <v>0.639180409795102</v>
       </c>
       <c r="O49" t="n">
-        <v>0.972513743128436</v>
+        <v>0.254372813593203</v>
       </c>
       <c r="P49" t="n">
-        <v>0.469265367316342</v>
+        <v>0.203398300849575</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.931534232883558</v>
+        <v>0.436281859070465</v>
       </c>
     </row>
     <row r="50">
@@ -3887,34 +3887,34 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I50" t="n">
-        <v>0.127501830029947</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0939530234882559</v>
+        <v>0.191904047976012</v>
       </c>
       <c r="N50" t="n">
-        <v>0.798100949525237</v>
+        <v>0.736131934032983</v>
       </c>
       <c r="O50" t="n">
-        <v>0.91904047976012</v>
+        <v>0.607696151924038</v>
       </c>
       <c r="P50" t="n">
-        <v>0.55272363818091</v>
+        <v>0.369315342328836</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.869065467266367</v>
+        <v>0.727136431784108</v>
       </c>
     </row>
     <row r="51">
@@ -3940,34 +3940,34 @@
         <v>0.833333333333333</v>
       </c>
       <c r="H51" t="n">
-        <v>0.966159499330321</v>
+        <v>0.983397488218171</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0578894771956845</v>
+        <v>0.27870827146302</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0.591105307782166</v>
+        <v>0.784928130624501</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0.347972440083505</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0889555222388806</v>
+        <v>0.0529735132433783</v>
       </c>
       <c r="N51" t="n">
-        <v>0.924537731134433</v>
+        <v>0.96751624187906</v>
       </c>
       <c r="O51" t="n">
-        <v>0.869065467266367</v>
+        <v>0.848575712143928</v>
       </c>
       <c r="P51" t="n">
-        <v>0.392303848075962</v>
+        <v>0.0474762618690655</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.905547226386807</v>
+        <v>0.964517741129435</v>
       </c>
     </row>
     <row r="52">
@@ -3993,34 +3993,34 @@
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>0.241255174106044</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J52" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>0.300466626758702</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M52" t="n">
-        <v>0.881059470264868</v>
+        <v>0.0584707646176912</v>
       </c>
       <c r="N52" t="n">
-        <v>0.156421789105447</v>
+        <v>0.987506246876562</v>
       </c>
       <c r="O52" t="n">
-        <v>0.107446276861569</v>
+        <v>0.791104447776112</v>
       </c>
       <c r="P52" t="n">
-        <v>0.386806596701649</v>
+        <v>0.0909545227386307</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.0909545227386307</v>
+        <v>0.907046476761619</v>
       </c>
     </row>
     <row r="53">
@@ -4046,34 +4046,34 @@
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.241255174106044</v>
+        <v>0.311977906248122</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0.548253916758134</v>
+        <v>0.502289493034358</v>
       </c>
       <c r="K53" t="n">
-        <v>0.300466626758702</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.967016491754123</v>
+        <v>0.948525737131434</v>
       </c>
       <c r="N53" t="n">
-        <v>0.0314842578710645</v>
+        <v>0.0329835082458771</v>
       </c>
       <c r="O53" t="n">
-        <v>0.0594702648675662</v>
+        <v>0.0719640179910045</v>
       </c>
       <c r="P53" t="n">
-        <v>0.690654672663668</v>
+        <v>0.627186406796602</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.0634682658670665</v>
+        <v>0.0674662668665667</v>
       </c>
     </row>
     <row r="54">
@@ -4099,34 +4099,34 @@
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>0.741426031795175</v>
+        <v>0.311977906248122</v>
       </c>
       <c r="I54" t="n">
-        <v>0.587058785749398</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>0.548253916758134</v>
+        <v>0.502289493034358</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L54" t="n">
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.320839580209895</v>
+        <v>0.713143428285857</v>
       </c>
       <c r="N54" t="n">
-        <v>0.666166916541729</v>
+        <v>0.252873563218391</v>
       </c>
       <c r="O54" t="n">
-        <v>0.854072963518241</v>
+        <v>0.35832083958021</v>
       </c>
       <c r="P54" t="n">
-        <v>0.806596701649175</v>
+        <v>0.891554222888556</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.756621689155422</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="55">
@@ -4152,34 +4152,34 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I55" t="n">
-        <v>0.127501830029947</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M55" t="n">
-        <v>0.0494752623688156</v>
+        <v>0.694652673663168</v>
       </c>
       <c r="N55" t="n">
-        <v>0.939030484757621</v>
+        <v>0.648675662168916</v>
       </c>
       <c r="O55" t="n">
-        <v>0.92703648175912</v>
+        <v>0.239380309845077</v>
       </c>
       <c r="P55" t="n">
-        <v>0.217391304347826</v>
+        <v>0.197901049475262</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.95352323838081</v>
+        <v>0.421789105447276</v>
       </c>
     </row>
     <row r="56">
@@ -4205,34 +4205,34 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I56" t="n">
-        <v>0.587058785749398</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0.502289493034358</v>
       </c>
       <c r="K56" t="n">
-        <v>0.300466626758702</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M56" t="n">
-        <v>0.537731134432784</v>
+        <v>0.516741629185407</v>
       </c>
       <c r="N56" t="n">
-        <v>0.367316341829085</v>
+        <v>0.51424287856072</v>
       </c>
       <c r="O56" t="n">
-        <v>0.1984007996002</v>
+        <v>0.52423788105947</v>
       </c>
       <c r="P56" t="n">
-        <v>0.640179910044978</v>
+        <v>0.526736631684158</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.343328335832084</v>
+        <v>0.460769615192404</v>
       </c>
     </row>
     <row r="57">
@@ -4261,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0.127501830029947</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
@@ -4270,22 +4270,22 @@
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M57" t="n">
-        <v>0.031984007996002</v>
+        <v>0.102948525737131</v>
       </c>
       <c r="N57" t="n">
-        <v>0.992003998000999</v>
+        <v>0.950024987506247</v>
       </c>
       <c r="O57" t="n">
-        <v>0.864567716141929</v>
+        <v>0.810594702648676</v>
       </c>
       <c r="P57" t="n">
-        <v>0.103448275862069</v>
+        <v>0.0464767616191904</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.979510244877561</v>
+        <v>0.915542228885557</v>
       </c>
     </row>
     <row r="58">
@@ -4311,34 +4311,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I58" t="n">
-        <v>0.587058785749398</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M58" t="n">
-        <v>0.456271864067966</v>
+        <v>0.426286856571714</v>
       </c>
       <c r="N58" t="n">
-        <v>0.400299850074962</v>
+        <v>0.622188905547226</v>
       </c>
       <c r="O58" t="n">
-        <v>0.609195402298851</v>
+        <v>0.470764617691154</v>
       </c>
       <c r="P58" t="n">
-        <v>0.750624687656172</v>
+        <v>0.253873063468266</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.540229885057471</v>
+        <v>0.551724137931034</v>
       </c>
     </row>
     <row r="59">
@@ -4364,34 +4364,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H59" t="n">
-        <v>0.241255174106044</v>
+        <v>0.311977906248122</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>0.107294511721661</v>
+        <v>0.502289493034358</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.754122938530735</v>
+        <v>0.705647176411794</v>
       </c>
       <c r="N59" t="n">
-        <v>0.138430784607696</v>
+        <v>0.144927536231884</v>
       </c>
       <c r="O59" t="n">
-        <v>0.435782108945527</v>
+        <v>0.324337831084458</v>
       </c>
       <c r="P59" t="n">
-        <v>0.966516741629185</v>
+        <v>0.868565717141429</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.230384807596202</v>
+        <v>0.169415292353823</v>
       </c>
     </row>
     <row r="60">
@@ -4417,34 +4417,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H60" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I60" t="n">
-        <v>0.587058785749398</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M60" t="n">
-        <v>0.443778110944528</v>
+        <v>0.430784607696152</v>
       </c>
       <c r="N60" t="n">
-        <v>0.427786106946527</v>
+        <v>0.604197901049475</v>
       </c>
       <c r="O60" t="n">
-        <v>0.631684157921039</v>
+        <v>0.47776111944028</v>
       </c>
       <c r="P60" t="n">
-        <v>0.749625187406297</v>
+        <v>0.253373313343328</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.559720139930035</v>
+        <v>0.551224387806097</v>
       </c>
     </row>
     <row r="61">
@@ -4470,34 +4470,34 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I61" t="n">
-        <v>0.587058785749398</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L61" t="n">
-        <v>0.28309325502308</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M61" t="n">
-        <v>0.589705147426287</v>
+        <v>0.522738630684658</v>
       </c>
       <c r="N61" t="n">
-        <v>0.661669165417291</v>
+        <v>0.534232883558221</v>
       </c>
       <c r="O61" t="n">
-        <v>0.563718140929535</v>
+        <v>0.455272363818091</v>
       </c>
       <c r="P61" t="n">
-        <v>0.345327336331834</v>
+        <v>0.24687656171914</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.60119940029985</v>
+        <v>0.52423788105947</v>
       </c>
     </row>
     <row r="62">
@@ -4526,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.127501830029947</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
@@ -4535,22 +4535,22 @@
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M62" t="n">
-        <v>0.047976011994003</v>
+        <v>0.0919540229885057</v>
       </c>
       <c r="N62" t="n">
-        <v>0.903548225887057</v>
+        <v>0.958020989505247</v>
       </c>
       <c r="O62" t="n">
-        <v>0.938530734632684</v>
+        <v>0.860569715142429</v>
       </c>
       <c r="P62" t="n">
-        <v>0.419290354822589</v>
+        <v>0.0344827586206897</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.954522738630685</v>
+        <v>0.946526736631684</v>
       </c>
     </row>
     <row r="63">
@@ -4579,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0454486292014263</v>
+        <v>0.503129728765281</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
@@ -4588,22 +4588,22 @@
         <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0.145949859984731</v>
       </c>
       <c r="M63" t="n">
-        <v>0.00549725137431284</v>
+        <v>0.0849575212393803</v>
       </c>
       <c r="N63" t="n">
-        <v>0.985007496251874</v>
+        <v>0.982008995502249</v>
       </c>
       <c r="O63" t="n">
-        <v>0.985507246376812</v>
+        <v>0.890554722638681</v>
       </c>
       <c r="P63" t="n">
-        <v>0.346326836581709</v>
+        <v>0.00849575212393803</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.996501749125437</v>
+        <v>0.975012493753123</v>
       </c>
     </row>
     <row r="64">
@@ -4629,34 +4629,34 @@
         <v>0.6</v>
       </c>
       <c r="H64" t="n">
-        <v>0.101025331722206</v>
+        <v>0.17404091711926</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0.753494913855398</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0163234852503589</v>
+        <v>0.0657541114556625</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0.841948471797413</v>
       </c>
       <c r="L64" t="n">
-        <v>0.632062839743509</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>0.955022488755622</v>
+        <v>0.865067466266867</v>
       </c>
       <c r="N64" t="n">
-        <v>0.0304847576211894</v>
+        <v>0.00749625187406297</v>
       </c>
       <c r="O64" t="n">
-        <v>0.11744127936032</v>
+        <v>0.319340329835082</v>
       </c>
       <c r="P64" t="n">
-        <v>0.862568715642179</v>
+        <v>0.990504747626187</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.0619690154922539</v>
+        <v>0.0779610194902549</v>
       </c>
     </row>
     <row r="65">
@@ -4682,34 +4682,34 @@
         <v>0.666666666666667</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0580492118486313</v>
+        <v>0.405092293166947</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>0.105948531795098</v>
+        <v>0.0792795667128238</v>
       </c>
       <c r="K65" t="n">
-        <v>0.510899041231745</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>0.668374777997246</v>
       </c>
       <c r="M65" t="n">
-        <v>0.952023988005997</v>
+        <v>0.895052473763118</v>
       </c>
       <c r="N65" t="n">
-        <v>0.0699650174912544</v>
+        <v>0.0834582708645677</v>
       </c>
       <c r="O65" t="n">
-        <v>0.2063968015992</v>
+        <v>0.356821589205397</v>
       </c>
       <c r="P65" t="n">
-        <v>0.911044477761119</v>
+        <v>0.811094452773613</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.124437781109445</v>
+        <v>0.145427286356822</v>
       </c>
     </row>
     <row r="66">
@@ -4738,7 +4738,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.587058785749398</v>
+        <v>0.0430857804408705</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
@@ -4747,22 +4747,22 @@
         <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>0.28309325502308</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>0.450274862568716</v>
+        <v>0.0264867566216892</v>
       </c>
       <c r="N66" t="n">
-        <v>0.784107946026987</v>
+        <v>0.897551224387806</v>
       </c>
       <c r="O66" t="n">
-        <v>0.633183408295852</v>
+        <v>0.972013993003498</v>
       </c>
       <c r="P66" t="n">
-        <v>0.156921539230385</v>
+        <v>0.452773613193403</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.679160419790105</v>
+        <v>0.968015992003998</v>
       </c>
     </row>
     <row r="67">
@@ -4788,34 +4788,34 @@
         <v>0.684210526315789</v>
       </c>
       <c r="H67" t="n">
-        <v>0.268283144867637</v>
+        <v>0.668086377084488</v>
       </c>
       <c r="I67" t="n">
-        <v>0.740870018549792</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>0.430666843426739</v>
+        <v>0.328564089830776</v>
       </c>
       <c r="K67" t="n">
-        <v>0.359943475692557</v>
+        <v>0.896059158137585</v>
       </c>
       <c r="L67" t="n">
-        <v>0.886018422162724</v>
+        <v>0.0677385570922769</v>
       </c>
       <c r="M67" t="n">
-        <v>0.557721139430285</v>
+        <v>0.697151424287856</v>
       </c>
       <c r="N67" t="n">
-        <v>0.197401299350325</v>
+        <v>0.534232883558221</v>
       </c>
       <c r="O67" t="n">
-        <v>0.264367816091954</v>
+        <v>0.543228385807096</v>
       </c>
       <c r="P67" t="n">
-        <v>0.263868065967017</v>
+        <v>0.0529735132433783</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.32183908045977</v>
+        <v>0.640179910044978</v>
       </c>
     </row>
     <row r="68">
@@ -4841,34 +4841,34 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>0.67463203654944</v>
+        <v>0.405092293166947</v>
       </c>
       <c r="I68" t="n">
-        <v>0.829723186836647</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>0.397515631749189</v>
+        <v>0.338403792644963</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0.707404412179439</v>
       </c>
       <c r="L68" t="n">
-        <v>0.486286777422666</v>
+        <v>0.668374777997246</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5952023988006</v>
+        <v>0.749125437281359</v>
       </c>
       <c r="N68" t="n">
-        <v>0.511244377811094</v>
+        <v>0.298850574712644</v>
       </c>
       <c r="O68" t="n">
-        <v>0.663168415792104</v>
+        <v>0.540729635182409</v>
       </c>
       <c r="P68" t="n">
-        <v>0.590704647676162</v>
+        <v>0.498750624687656</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.569215392303848</v>
+        <v>0.340829585207396</v>
       </c>
     </row>
     <row r="69">
@@ -4894,34 +4894,34 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I69" t="n">
-        <v>0.587058785749398</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>0.548253916758134</v>
+        <v>0.502289493034358</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0.423888394598551</v>
       </c>
       <c r="M69" t="n">
-        <v>0.545227386306847</v>
+        <v>0.572713643178411</v>
       </c>
       <c r="N69" t="n">
-        <v>0.438280859570215</v>
+        <v>0.383308345827086</v>
       </c>
       <c r="O69" t="n">
-        <v>0.609195402298851</v>
+        <v>0.589705147426287</v>
       </c>
       <c r="P69" t="n">
-        <v>0.815092453773113</v>
+        <v>0.212893553223388</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.561219390304848</v>
+        <v>0.529235382308846</v>
       </c>
     </row>
     <row r="70">
@@ -4947,13 +4947,13 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I70" t="n">
-        <v>0.587058785749398</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J70" t="n">
-        <v>0.548253916758134</v>
+        <v>0.502289493034358</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
@@ -4962,19 +4962,19 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0.590704647676162</v>
+        <v>0.225887056471764</v>
       </c>
       <c r="N70" t="n">
-        <v>0.493253373313343</v>
+        <v>0.648675662168916</v>
       </c>
       <c r="O70" t="n">
-        <v>0.711644177911045</v>
+        <v>0.879060469765117</v>
       </c>
       <c r="P70" t="n">
-        <v>0.934032983508246</v>
+        <v>0.584207896051974</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.618190904547726</v>
+        <v>0.827086456771614</v>
       </c>
     </row>
     <row r="71">
@@ -5000,34 +5000,34 @@
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>0.741426031795175</v>
+        <v>0.805405031532507</v>
       </c>
       <c r="I71" t="n">
-        <v>0.587058785749398</v>
+        <v>0.37256527792988</v>
       </c>
       <c r="J71" t="n">
-        <v>0.548253916758134</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0.217891054472764</v>
+        <v>0.488255872063968</v>
       </c>
       <c r="N71" t="n">
+        <v>0.611194402798601</v>
+      </c>
+      <c r="O71" t="n">
         <v>0.677161419290355</v>
       </c>
-      <c r="O71" t="n">
-        <v>0.866066966516742</v>
-      </c>
       <c r="P71" t="n">
-        <v>0.754122938530735</v>
+        <v>0.651174412793603</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.772613693153423</v>
+        <v>0.623188405797101</v>
       </c>
     </row>
     <row r="72">
@@ -5053,34 +5053,34 @@
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0.741426031795175</v>
+        <v>0.311977906248122</v>
       </c>
       <c r="I72" t="n">
-        <v>0.587058785749398</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>0.548253916758134</v>
+        <v>0.502289493034358</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0.458829060793224</v>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>0.174912543728136</v>
+        <v>0.649175412293853</v>
       </c>
       <c r="N72" t="n">
-        <v>0.31384307846077</v>
+        <v>0.0709645177411294</v>
       </c>
       <c r="O72" t="n">
-        <v>0.656671664167916</v>
+        <v>0.145427286356822</v>
       </c>
       <c r="P72" t="n">
-        <v>0.683158420789605</v>
+        <v>0.859570214892554</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.480259870064968</v>
+        <v>0.063968015992004</v>
       </c>
     </row>
   </sheetData>
